--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.3437723210732</v>
+        <v>563.1598679985283</v>
       </c>
       <c r="E2" t="n">
-        <v>11630.45608684529</v>
+        <v>12287.60408158444</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6061292343090758</v>
+        <v>0.5874422208075074</v>
       </c>
       <c r="G2" t="n">
-        <v>0.495031810930434</v>
+        <v>0.4951623614470049</v>
       </c>
       <c r="H2" t="n">
-        <v>1.224424816598815</v>
+        <v>1.186362830750776</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.9344957979635</v>
+        <v>219.5098349941483</v>
       </c>
       <c r="E3" t="n">
-        <v>4381.76441512388</v>
+        <v>5124.970315043257</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2495682659244323</v>
+        <v>0.2221013535168024</v>
       </c>
       <c r="G3" t="n">
-        <v>0.59360445241622</v>
+        <v>0.5938921846715122</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4204285613232589</v>
+        <v>0.3739758819012729</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890660483943662</v>
+        <v>0.8907172720756861</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06801223110577</v>
+        <v>1.068316309607661</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.15380731334123</v>
+        <v>36.78402577351495</v>
       </c>
       <c r="E4" t="n">
-        <v>1097.842698073965</v>
+        <v>450.7401436576145</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3278965649404926</v>
+        <v>-0.3371412784600496</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5573900336671642</v>
+        <v>0.5574295748746062</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5882713093795472</v>
+        <v>-0.6048141212024668</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7361607545566436</v>
+        <v>0.7362594246611445</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8288935351357356</v>
+        <v>0.8288448598696826</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.62708709850867</v>
+        <v>36.10434147175558</v>
       </c>
       <c r="E5" t="n">
-        <v>1500.429021501373</v>
+        <v>1638.485722537802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7167172282876826</v>
+        <v>0.6770921536802064</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100617279510825</v>
+        <v>1.100894555901165</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6511956895736101</v>
+        <v>0.6150381524286453</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.473702256675073</v>
+        <v>0.4739755795502036</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053194719062456</v>
+        <v>1.053789980385583</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.93274429141267</v>
+        <v>10.70030318257916</v>
       </c>
       <c r="E6" t="n">
-        <v>344.9643607494137</v>
+        <v>380.7739436740814</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.477933172425856</v>
+        <v>-0.4919945308768549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8101413070995591</v>
+        <v>0.8104379229621467</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5899380370283012</v>
+        <v>-0.6070724443380157</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6665902690300181</v>
+        <v>0.6668023982612741</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090904260954081</v>
+        <v>1.091363142169847</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.75343585773026</v>
+        <v>10.52539743966875</v>
       </c>
       <c r="E7" t="n">
-        <v>192.5932166563</v>
+        <v>218.8529177104667</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3085453938602553</v>
+        <v>-0.3276558456388384</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7099926904221429</v>
+        <v>0.7103317320394359</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4345754513004949</v>
+        <v>-0.4612715874287421</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501650341769744</v>
+        <v>0.7503344270438244</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075914070804585</v>
+        <v>1.076387049317157</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.621975408729311</v>
+        <v>9.428652804890202</v>
       </c>
       <c r="E8" t="n">
-        <v>375.8343645366357</v>
+        <v>416.3064738275572</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3401916964062384</v>
+        <v>-0.3574700696182836</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164135783241472</v>
+        <v>1.164280738116335</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.29222681864395</v>
+        <v>-0.3070308199005566</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372014071137899</v>
+        <v>0.7372983792648081</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733631089008396</v>
+        <v>1.733617835398181</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.990230223982651</v>
+        <v>6.914019056413516</v>
       </c>
       <c r="E9" t="n">
-        <v>251.3115576979156</v>
+        <v>256.6266860828266</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3248215395012781</v>
+        <v>0.3067794607627357</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812738934664793</v>
+        <v>0.4813763024922337</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6749203393553735</v>
+        <v>0.6372965581696559</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6732710835610896</v>
+        <v>0.6734447950612041</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6545595426177087</v>
+        <v>0.6546950871464778</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.783040476377229</v>
+        <v>6.60586139213844</v>
       </c>
       <c r="E10" t="n">
-        <v>524.6715481241187</v>
+        <v>570.4218955186223</v>
       </c>
       <c r="F10" t="n">
-        <v>0.995702066627365</v>
+        <v>0.9343752002586445</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8164349371719651</v>
+        <v>0.8169193505746438</v>
       </c>
       <c r="H10" t="n">
-        <v>1.21957307470986</v>
+        <v>1.143779002910604</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6636765926213016</v>
+        <v>0.6639006710933369</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094573611705574</v>
+        <v>1.095303979669878</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.417977282132367</v>
+        <v>6.263512917893096</v>
       </c>
       <c r="E11" t="n">
-        <v>226.7286033416975</v>
+        <v>246.7468437281841</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3017251919829453</v>
+        <v>-0.3236345750097638</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9522582499657136</v>
+        <v>0.952576862817343</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3168522740483572</v>
+        <v>-0.3397464158982212</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7131438967644133</v>
+        <v>0.7133260993665823</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371825293065948</v>
+        <v>1.372272997314791</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.187492827920792</v>
+        <v>6.249184593364917</v>
       </c>
       <c r="E12" t="n">
-        <v>106.7022957129641</v>
+        <v>114.6374177954719</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2907710312769991</v>
+        <v>-0.3029354907425026</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6539281215821555</v>
+        <v>0.6540560918210035</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4446528933080429</v>
+        <v>-0.4631643899211742</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887154189415151</v>
+        <v>0.78882287492626</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041878887342428</v>
+        <v>1.041949968098487</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.796870321419521</v>
+        <v>4.720741868686981</v>
       </c>
       <c r="E13" t="n">
-        <v>339.5245834078123</v>
+        <v>329.744783678729</v>
       </c>
       <c r="F13" t="n">
-        <v>1.773089170510356</v>
+        <v>1.709043499340648</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8566592962004813</v>
+        <v>0.8570543929578168</v>
       </c>
       <c r="H13" t="n">
-        <v>2.069771703143236</v>
+        <v>1.99408988902384</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6017419327019776</v>
+        <v>0.6020102954813282</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041322616407037</v>
+        <v>1.041992704858134</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.439212440149912</v>
+        <v>4.379938309670658</v>
       </c>
       <c r="E14" t="n">
-        <v>109.8857176906806</v>
+        <v>123.7679594774713</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4187343147410901</v>
+        <v>-0.4289714814948847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8444767198112655</v>
+        <v>0.8445868219920771</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4958506314237701</v>
+        <v>-0.5079069082360236</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600692505851143</v>
+        <v>0.7601507317125724</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296605134035969</v>
+        <v>1.296571267767463</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.10382464436727</v>
+        <v>4.012669142801838</v>
       </c>
       <c r="E15" t="n">
-        <v>138.8507139972543</v>
+        <v>147.0058358374314</v>
       </c>
       <c r="F15" t="n">
-        <v>0.493405785218056</v>
+        <v>0.4420426157594448</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9551794754468873</v>
+        <v>0.9556262895422625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5165581944557726</v>
+        <v>0.4625684962802559</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5135299600779063</v>
+        <v>0.5138640085036492</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9908722370215647</v>
+        <v>0.9917190683488815</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.068459955480536</v>
+        <v>4.001238413376695</v>
       </c>
       <c r="E16" t="n">
-        <v>206.2749064127478</v>
+        <v>219.1471360167294</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04953394247403642</v>
+        <v>-0.06723811120960366</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7896798786890076</v>
+        <v>0.7898111611721306</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06272661088474298</v>
+        <v>-0.08513188280324878</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7130455253226519</v>
+        <v>0.7131694835801767</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137457616871534</v>
+        <v>1.13754449407858</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.763206611504946</v>
+        <v>3.707383564674249</v>
       </c>
       <c r="E17" t="n">
-        <v>143.3659984095891</v>
+        <v>143.3834107747459</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08181879866603603</v>
+        <v>-0.09920247304226626</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7509007903403961</v>
+        <v>0.7510921436574766</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1089608636967157</v>
+        <v>-0.1320776337230681</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7207187312087425</v>
+        <v>0.720865424896671</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093239369527759</v>
+        <v>1.093452167268869</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.077163920126518</v>
+        <v>3.025361366592443</v>
       </c>
       <c r="E18" t="n">
-        <v>64.38089509752021</v>
+        <v>68.61624549591259</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4703647251856231</v>
+        <v>-0.4816093017394634</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407215379009352</v>
+        <v>0.7408440087487265</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6350088408642036</v>
+        <v>-0.6500819282495025</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643771452218265</v>
+        <v>0.7645069925068829</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143745921056786</v>
+        <v>1.143827700049954</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.960823780264001</v>
+        <v>2.943013195434335</v>
       </c>
       <c r="E19" t="n">
-        <v>61.86233559122608</v>
+        <v>63.20459315654885</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1091666652213865</v>
+        <v>0.1018626488731686</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4782067287001115</v>
+        <v>0.4782063883449368</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2282834152462252</v>
+        <v>0.2130098036241493</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172763606471526</v>
+        <v>0.7172413615521981</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6928976571309646</v>
+        <v>0.6926806796808413</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.628655993505296</v>
+        <v>2.567737985350148</v>
       </c>
       <c r="E20" t="n">
-        <v>126.4733793757715</v>
+        <v>131.7103833585542</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3021925395572997</v>
+        <v>-0.3237031416707082</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7731684412075419</v>
+        <v>0.7735991109165821</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3908495528934581</v>
+        <v>-0.4184378408697699</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320498133980246</v>
+        <v>0.7322249258671234</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143356448239972</v>
+        <v>1.143965284409831</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>563.1598679985283</v>
+        <v>561.2635178091818</v>
       </c>
       <c r="E2" t="n">
-        <v>12287.60408158444</v>
+        <v>12905.7215470341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5874422208075074</v>
+        <v>0.5787569673870119</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4951623614470049</v>
+        <v>0.4952924949786383</v>
       </c>
       <c r="H2" t="n">
-        <v>1.186362830750776</v>
+        <v>1.168515520131137</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219.5098349941483</v>
+        <v>220.797234880432</v>
       </c>
       <c r="E3" t="n">
-        <v>5124.970315043257</v>
+        <v>5478.424432380467</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2221013535168024</v>
+        <v>0.2172685208444616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5938921846715122</v>
+        <v>0.5940060472554103</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3739758819012729</v>
+        <v>0.3657681968867913</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907172720756861</v>
+        <v>0.8907900272631667</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068316309607661</v>
+        <v>1.06832764153221</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.78402577351495</v>
+        <v>36.75576875982053</v>
       </c>
       <c r="E4" t="n">
-        <v>450.7401436576145</v>
+        <v>435.9800082382589</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3371412784600496</v>
+        <v>-0.338248495782999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5574295748746062</v>
+        <v>0.557451363445577</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6048141212024668</v>
+        <v>-0.6067766947277753</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7362594246611445</v>
+        <v>0.7362525291751951</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8288448598696826</v>
+        <v>0.8286517166925138</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.10434147175558</v>
+        <v>36.27075974750539</v>
       </c>
       <c r="E5" t="n">
-        <v>1638.485722537802</v>
+        <v>1662.199374064923</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6770921536802064</v>
+        <v>0.6914745651460379</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100894555901165</v>
+        <v>1.100752187771047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6150381524286453</v>
+        <v>0.6281836846004638</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4739755795502036</v>
+        <v>0.4739151495490974</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053789980385583</v>
+        <v>1.053242564692023</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.70030318257916</v>
+        <v>10.68185210371526</v>
       </c>
       <c r="E6" t="n">
-        <v>380.7739436740814</v>
+        <v>403.0054140552663</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4919945308768549</v>
+        <v>-0.4950078370707751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8104379229621467</v>
+        <v>0.8105890137249195</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6070724443380157</v>
+        <v>-0.6106767161771086</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6668023982612741</v>
+        <v>0.6669596205132963</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091363142169847</v>
+        <v>1.091537114870954</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.52539743966875</v>
+        <v>10.5403451851956</v>
       </c>
       <c r="E7" t="n">
-        <v>218.8529177104667</v>
+        <v>226.9040521709681</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3276558456388384</v>
+        <v>-0.3285483632482094</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7103317320394359</v>
+        <v>0.7103673432503643</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4612715874287421</v>
+        <v>-0.4625048805662997</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503344270438244</v>
+        <v>0.7504434616547523</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076387049317157</v>
+        <v>1.076314568704065</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.428652804890202</v>
+        <v>9.432415728396876</v>
       </c>
       <c r="E8" t="n">
-        <v>416.3064738275572</v>
+        <v>417.2687909503089</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3574700696182836</v>
+        <v>-0.3603996510463586</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164280738116335</v>
+        <v>1.164349495825066</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3070308199005566</v>
+        <v>-0.3095287560467204</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372983792648081</v>
+        <v>0.7373213924422126</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733617835398181</v>
+        <v>1.733318796983087</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.914019056413516</v>
+        <v>6.915839843789024</v>
       </c>
       <c r="E9" t="n">
-        <v>256.6266860828266</v>
+        <v>259.9794602444616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3067794607627357</v>
+        <v>0.3031784583826393</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4813763024922337</v>
+        <v>0.4814313037282125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6372965581696559</v>
+        <v>0.6297439656183966</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6734447950612041</v>
+        <v>0.6735475028230136</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6546950871464778</v>
+        <v>0.6546976901415613</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.60586139213844</v>
+        <v>6.600152613029897</v>
       </c>
       <c r="E10" t="n">
-        <v>570.4218955186223</v>
+        <v>590.3199104650042</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9343752002586445</v>
+        <v>0.9209703692670075</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8169193505746438</v>
+        <v>0.8171415206548077</v>
       </c>
       <c r="H10" t="n">
-        <v>1.143779002910604</v>
+        <v>1.127063484093915</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6639006710933369</v>
+        <v>0.6641036652080853</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095303979669878</v>
+        <v>1.095648903147565</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.263512917893096</v>
+        <v>6.253014788631258</v>
       </c>
       <c r="E11" t="n">
-        <v>246.7468437281841</v>
+        <v>255.8342749097501</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3236345750097638</v>
+        <v>-0.3279152790761067</v>
       </c>
       <c r="G11" t="n">
-        <v>0.952576862817343</v>
+        <v>0.9527303828467482</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3397464158982212</v>
+        <v>-0.3441847609565042</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133260993665823</v>
+        <v>0.7134511565577296</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372272997314791</v>
+        <v>1.372374103021725</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.249184593364917</v>
+        <v>6.091779196231098</v>
       </c>
       <c r="E12" t="n">
-        <v>114.6374177954719</v>
+        <v>118.4453727383718</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3029354907425026</v>
+        <v>-0.306243944133641</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6540560918210035</v>
+        <v>0.6541491645292993</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4631643899211742</v>
+        <v>-0.4681561343183896</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.78882287492626</v>
+        <v>0.7888927265439448</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041949968098487</v>
+        <v>1.041916692063383</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.720741868686981</v>
+        <v>4.714668771149109</v>
       </c>
       <c r="E13" t="n">
-        <v>329.744783678729</v>
+        <v>327.8542846627178</v>
       </c>
       <c r="F13" t="n">
-        <v>1.709043499340648</v>
+        <v>1.701620600772102</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8570543929578168</v>
+        <v>0.8571302549762533</v>
       </c>
       <c r="H13" t="n">
-        <v>1.99408988902384</v>
+        <v>1.985253222474622</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020102954813282</v>
+        <v>0.6021834685950108</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041992704858134</v>
+        <v>1.042110823830649</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.379938309670658</v>
+        <v>4.353556045005568</v>
       </c>
       <c r="E14" t="n">
-        <v>123.7679594774713</v>
+        <v>127.1226181866827</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4289714814948847</v>
+        <v>-0.4343727416677624</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445868219920771</v>
+        <v>0.8447558339687485</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5079069082360236</v>
+        <v>-0.5141991616998195</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601507317125724</v>
+        <v>0.7602623638840545</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296571267767463</v>
+        <v>1.296680393401935</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.012669142801838</v>
+        <v>4.008461986194387</v>
       </c>
       <c r="E15" t="n">
-        <v>147.0058358374314</v>
+        <v>152.0640731245471</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4420426157594448</v>
+        <v>0.4459776780976346</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9556262895422625</v>
+        <v>0.9555589278400258</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4625684962802559</v>
+        <v>0.4667191788011817</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5138640085036492</v>
+        <v>0.5139755510401176</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9917190683488815</v>
+        <v>0.9916038128319784</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.001238413376695</v>
+        <v>3.966341414361243</v>
       </c>
       <c r="E16" t="n">
-        <v>219.1471360167294</v>
+        <v>229.9821538851635</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06723811120960366</v>
+        <v>-0.08353195011993297</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7898111611721306</v>
+        <v>0.7902243658481526</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08513188280324878</v>
+        <v>-0.1057066242576279</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131694835801767</v>
+        <v>0.7133956799425033</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13754449407858</v>
+        <v>1.138201475888889</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.707383564674249</v>
+        <v>3.705368248834039</v>
       </c>
       <c r="E17" t="n">
-        <v>143.3834107747459</v>
+        <v>149.5000591904293</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.09920247304226626</v>
+        <v>-0.1042337904574507</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7510921436574766</v>
+        <v>0.7512141795994041</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1320776337230681</v>
+        <v>-0.1387537579669156</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.720865424896671</v>
+        <v>0.7209774981678725</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093452167268869</v>
+        <v>1.09351247048306</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.025361366592443</v>
+        <v>3.011156710430971</v>
       </c>
       <c r="E18" t="n">
-        <v>68.61624549591259</v>
+        <v>70.21220922719237</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4816093017394634</v>
+        <v>-0.4861059938030704</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7408440087487265</v>
+        <v>0.7410212179222577</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6500819282495025</v>
+        <v>-0.6559947030478538</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645069925068829</v>
+        <v>0.7646271419487143</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143827700049954</v>
+        <v>1.143980459481198</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.943013195434335</v>
+        <v>2.937051248766904</v>
       </c>
       <c r="E19" t="n">
-        <v>63.20459315654885</v>
+        <v>66.45358539035669</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1018626488731686</v>
+        <v>0.09639254300514866</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4782063883449368</v>
+        <v>0.4782505384847085</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2130098036241493</v>
+        <v>0.2015523982692404</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7172413615521981</v>
+        <v>0.7173327860969236</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926806796808413</v>
+        <v>0.6926508976042254</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.567737985350148</v>
+        <v>2.575861407978183</v>
       </c>
       <c r="E20" t="n">
-        <v>131.7103833585542</v>
+        <v>132.2184470270295</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3237031416707082</v>
+        <v>-0.3222078631158145</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7735991109165821</v>
+        <v>0.7735392957923792</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4184378408697699</v>
+        <v>-0.4165371621951786</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322249258671234</v>
+        <v>0.7323257558442294</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143965284409831</v>
+        <v>1.143733763805162</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>561.2635178091818</v>
+        <v>562.6115442724069</v>
       </c>
       <c r="E2" t="n">
-        <v>12905.7215470341</v>
+        <v>13033.43086053953</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5787569673870119</v>
+        <v>0.5841464914738117</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4952924949786383</v>
+        <v>0.4952065374644309</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168515520131137</v>
+        <v>1.179601736408355</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.797234880432</v>
+        <v>220.0278086843567</v>
       </c>
       <c r="E3" t="n">
-        <v>5478.424432380467</v>
+        <v>5549.440578212915</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2172685208444616</v>
+        <v>0.2249873052862965</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5940060472554103</v>
+        <v>0.5938332541003811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3657681968867913</v>
+        <v>0.3788728632705787</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907900272631667</v>
+        <v>0.8907475981007883</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06832764153221</v>
+        <v>1.068151376737999</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.75576875982053</v>
+        <v>37.00614116210963</v>
       </c>
       <c r="E4" t="n">
-        <v>435.9800082382589</v>
+        <v>450.3388626056268</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.338248495782999</v>
+        <v>-0.3327078001211096</v>
       </c>
       <c r="G4" t="n">
-        <v>0.557451363445577</v>
+        <v>0.5573789399166467</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6067766947277753</v>
+        <v>-0.5969149106546157</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7362525291751951</v>
+        <v>0.7360371005394883</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8286517166925138</v>
+        <v>0.8284454016673584</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.27075974750539</v>
+        <v>36.23933127086826</v>
       </c>
       <c r="E5" t="n">
-        <v>1662.199374064923</v>
+        <v>1676.265855122486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6914745651460379</v>
+        <v>0.6924562982259104</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100752187771047</v>
+        <v>1.100744209369868</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6281836846004638</v>
+        <v>0.6290801190063166</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4739151495490974</v>
+        <v>0.4738927960815195</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053242564692023</v>
+        <v>1.05336806298987</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.68185210371526</v>
+        <v>10.72174536871091</v>
       </c>
       <c r="E6" t="n">
-        <v>403.0054140552663</v>
+        <v>406.1945055697069</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4950078370707751</v>
+        <v>-0.4907524598248586</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8105890137249195</v>
+        <v>0.8103846870794321</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6106767161771086</v>
+        <v>-0.6055796310681721</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6669596205132963</v>
+        <v>0.6668157384345273</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091537114870954</v>
+        <v>1.091215932442569</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.5403451851956</v>
+        <v>10.6504540882796</v>
       </c>
       <c r="E7" t="n">
-        <v>226.9040521709681</v>
+        <v>229.4058747075745</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3285483632482094</v>
+        <v>-0.3163251126459844</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7103673432503643</v>
+        <v>0.7100334630380056</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4625048805662997</v>
+        <v>-0.4455073304468364</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7504434616547523</v>
+        <v>0.7501597596238017</v>
       </c>
       <c r="N7" t="n">
-        <v>1.076314568704065</v>
+        <v>1.075588651726358</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.432415728396876</v>
+        <v>9.50939016072067</v>
       </c>
       <c r="E8" t="n">
-        <v>417.2687909503089</v>
+        <v>425.1849688437369</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3603996510463586</v>
+        <v>-0.3523352843375736</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164349495825066</v>
+        <v>1.164191266808599</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3095287560467204</v>
+        <v>-0.3026438132485147</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7373213924422126</v>
+        <v>0.7371918009763024</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733318796983087</v>
+        <v>1.733079415820834</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.915839843789024</v>
+        <v>6.974951533490295</v>
       </c>
       <c r="E9" t="n">
-        <v>259.9794602444616</v>
+        <v>261.6230141767549</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3031784583826393</v>
+        <v>0.3218855078963343</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4814313037282125</v>
+        <v>0.4812709550167137</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6297439656183966</v>
+        <v>0.6688238808950266</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6735475028230136</v>
+        <v>0.6730598373089554</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6546976901415613</v>
+        <v>0.6541192940295975</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.600152613029897</v>
+        <v>6.643630203757324</v>
       </c>
       <c r="E10" t="n">
-        <v>590.3199104650042</v>
+        <v>577.9497521297754</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9209703692670075</v>
+        <v>0.9383726168061925</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8171415206548077</v>
+        <v>0.8168612258348862</v>
       </c>
       <c r="H10" t="n">
-        <v>1.127063484093915</v>
+        <v>1.148754019811766</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6641036652080853</v>
+        <v>0.6639552166399424</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095648903147565</v>
+        <v>1.095218320301206</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.253014788631258</v>
+        <v>6.286370194023998</v>
       </c>
       <c r="E11" t="n">
-        <v>255.8342749097501</v>
+        <v>261.4243131877716</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3279152790761067</v>
+        <v>-0.3205536389750143</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9527303828467482</v>
+        <v>0.9524849534883089</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3441847609565042</v>
+        <v>-0.3365445698654272</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7134511565577296</v>
+        <v>0.7133167467411397</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372374103021725</v>
+        <v>1.372000199797376</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.091779196231098</v>
+        <v>6.131476340790977</v>
       </c>
       <c r="E12" t="n">
-        <v>118.4453727383718</v>
+        <v>120.7893934588445</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.306243944133641</v>
+        <v>-0.2998072411508066</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6541491645292993</v>
+        <v>0.6539910759371788</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4681561343183896</v>
+        <v>-0.4584271134299172</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888927265439448</v>
+        <v>0.7887465302185999</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041916692063383</v>
+        <v>1.041652629588779</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.714668771149109</v>
+        <v>4.721409619562107</v>
       </c>
       <c r="E13" t="n">
-        <v>327.8542846627178</v>
+        <v>312.3075985215337</v>
       </c>
       <c r="F13" t="n">
-        <v>1.701620600772102</v>
+        <v>1.706073730605743</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8571302549762533</v>
+        <v>0.8570839902350758</v>
       </c>
       <c r="H13" t="n">
-        <v>1.985253222474622</v>
+        <v>1.990556059900048</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021834685950108</v>
+        <v>0.6020772233752364</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042110823830649</v>
+        <v>1.042051568386589</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.353556045005568</v>
+        <v>4.377069529676555</v>
       </c>
       <c r="E14" t="n">
-        <v>127.1226181866827</v>
+        <v>127.3007907711024</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4343727416677624</v>
+        <v>-0.4283705522414626</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8447558339687485</v>
+        <v>0.8445727735072812</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5141991616998195</v>
+        <v>-0.5072038380571471</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602623638840545</v>
+        <v>0.7601253955793115</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296680393401935</v>
+        <v>1.296390828854617</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.008461986194387</v>
+        <v>4.017797693880548</v>
       </c>
       <c r="E15" t="n">
-        <v>152.0640731245471</v>
+        <v>154.0514650858856</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4459776780976346</v>
+        <v>0.4525420506079885</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9555589278400258</v>
+        <v>0.9554588711311052</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4667191788011817</v>
+        <v>0.4736384414666155</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139755510401176</v>
+        <v>0.5138466983622132</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9916038128319784</v>
+        <v>0.9914234752744348</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.966341414361243</v>
+        <v>3.986851566780058</v>
       </c>
       <c r="E16" t="n">
-        <v>229.9821538851635</v>
+        <v>235.7337887749929</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.08353195011993297</v>
+        <v>-0.07422994909455738</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7902243658481526</v>
+        <v>0.7899539354291416</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1057066242576279</v>
+        <v>-0.09396744008146758</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7133956799425033</v>
+        <v>0.7132583673894424</v>
       </c>
       <c r="N16" t="n">
-        <v>1.138201475888889</v>
+        <v>1.13779042009825</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.705368248834039</v>
+        <v>3.706266990702266</v>
       </c>
       <c r="E17" t="n">
-        <v>149.5000591904293</v>
+        <v>158.5327574149704</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1042337904574507</v>
+        <v>-0.1010667430402775</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7512141795994041</v>
+        <v>0.7511338555365111</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1387537579669156</v>
+        <v>-0.134552240316859</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7209774981678725</v>
+        <v>0.720904367524163</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09351247048306</v>
+        <v>1.093474411351907</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.011156710430971</v>
+        <v>3.03833502816753</v>
       </c>
       <c r="E18" t="n">
-        <v>70.21220922719237</v>
+        <v>71.05109211383257</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4861059938030704</v>
+        <v>-0.4793177678038928</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7410212179222577</v>
+        <v>0.7407819960238377</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6559947030478538</v>
+        <v>-0.6470429497161656</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7646271419487143</v>
+        <v>0.7644357156981753</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143980459481198</v>
+        <v>1.14352330283499</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.937051248766904</v>
+        <v>2.954559323246497</v>
       </c>
       <c r="E19" t="n">
-        <v>66.45358539035669</v>
+        <v>67.91917420880405</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09639254300514866</v>
+        <v>0.1073395335216012</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4782505384847085</v>
+        <v>0.478200299652031</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2015523982692404</v>
+        <v>0.2244656341698411</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173327860969236</v>
+        <v>0.7169692018324033</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6926508976042254</v>
+        <v>0.6923472555774952</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.575861407978183</v>
+        <v>2.58550503995294</v>
       </c>
       <c r="E20" t="n">
-        <v>132.2184470270295</v>
+        <v>131.9305548313361</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3222078631158145</v>
+        <v>-0.3182164331458633</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7735392957923792</v>
+        <v>0.7734016066593395</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4165371621951786</v>
+        <v>-0.4114504423133791</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7323257558442294</v>
+        <v>0.7322305982284053</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143733763805162</v>
+        <v>1.143580058564259</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>562.6115442724069</v>
+        <v>562.5512009818385</v>
       </c>
       <c r="E2" t="n">
-        <v>13033.43086053953</v>
+        <v>13318.23541538972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5841464914738117</v>
+        <v>0.5853992362708655</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4952065374644309</v>
+        <v>0.49518899634524</v>
       </c>
       <c r="H2" t="n">
-        <v>1.179601736408355</v>
+        <v>1.182173353187218</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.0278086843567</v>
+        <v>222.1536773916811</v>
       </c>
       <c r="E3" t="n">
-        <v>5549.440578212915</v>
+        <v>5678.414804681795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2249873052862965</v>
+        <v>0.2295869514238134</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5938332541003811</v>
+        <v>0.5937533092906018</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3788728632705787</v>
+        <v>0.3866706051678546</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907475981007883</v>
+        <v>0.8907252105054521</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068151376737999</v>
+        <v>1.068018565253936</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.00614116210963</v>
+        <v>37.73248978644512</v>
       </c>
       <c r="E4" t="n">
-        <v>450.3388626056268</v>
+        <v>687.9456795702848</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3327078001211096</v>
+        <v>-0.3126664674597445</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5573789399166467</v>
+        <v>0.5578740799402215</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5969149106546157</v>
+        <v>-0.5604606464119071</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7360371005394883</v>
+        <v>0.7342373026236262</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8284454016673584</v>
+        <v>0.8271830809692885</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.23933127086826</v>
+        <v>36.41429103030152</v>
       </c>
       <c r="E5" t="n">
-        <v>1676.265855122486</v>
+        <v>1676.688113474105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6924562982259104</v>
+        <v>0.7022814320858282</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100744209369868</v>
+        <v>1.100676564083331</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6290801190063166</v>
+        <v>0.6380452305448188</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4738927960815195</v>
+        <v>0.4738034228363468</v>
       </c>
       <c r="N5" t="n">
-        <v>1.05336806298987</v>
+        <v>1.053141986892708</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.72174536871091</v>
+        <v>10.79384657532092</v>
       </c>
       <c r="E6" t="n">
-        <v>406.1945055697069</v>
+        <v>411.7530853584049</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4907524598248586</v>
+        <v>-0.4859545432093765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8103846870794321</v>
+        <v>0.8102284294768416</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6055796310681721</v>
+        <v>-0.5997747370123184</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6668157384345273</v>
+        <v>0.6666857300379516</v>
       </c>
       <c r="N6" t="n">
-        <v>1.091215932442569</v>
+        <v>1.090831452213192</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.6504540882796</v>
+        <v>10.67671581809037</v>
       </c>
       <c r="E7" t="n">
-        <v>229.4058747075745</v>
+        <v>240.8327722743505</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3163251126459844</v>
+        <v>-0.3145317418352761</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100334630380056</v>
+        <v>0.7100122738635899</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4455073304468364</v>
+        <v>-0.4429947951797029</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501597596238017</v>
+        <v>0.7501136948627734</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075588651726358</v>
+        <v>1.075528604384459</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.50939016072067</v>
+        <v>9.53127140435288</v>
       </c>
       <c r="E8" t="n">
-        <v>425.1849688437369</v>
+        <v>428.7338714297467</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3523352843375736</v>
+        <v>-0.3479259440856937</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164191266808599</v>
+        <v>1.164145838159876</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3026438132485147</v>
+        <v>-0.2988680049190811</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7371918009763024</v>
+        <v>0.7371063687134948</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733079415820834</v>
+        <v>1.732872333093397</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.974951533490295</v>
+        <v>6.997349618932689</v>
       </c>
       <c r="E9" t="n">
-        <v>261.6230141767549</v>
+        <v>252.6008603181862</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3218855078963343</v>
+        <v>0.3250474553394318</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812709550167137</v>
+        <v>0.4812744342457686</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6688238808950266</v>
+        <v>0.6753889926624326</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6730598373089554</v>
+        <v>0.6729696845442534</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6541192940295975</v>
+        <v>0.6540595743928475</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.643630203757324</v>
+        <v>6.659136076531319</v>
       </c>
       <c r="E10" t="n">
-        <v>577.9497521297754</v>
+        <v>578.6940957874275</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9383726168061925</v>
+        <v>0.9469454310732499</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8168612258348862</v>
+        <v>0.8167491268500712</v>
       </c>
       <c r="H10" t="n">
-        <v>1.148754019811766</v>
+        <v>1.159407950303299</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6639552166399424</v>
+        <v>0.6639101369463956</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095218320301206</v>
+        <v>1.095032459646641</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.286370194023998</v>
+        <v>6.345287972850897</v>
       </c>
       <c r="E11" t="n">
-        <v>261.4243131877716</v>
+        <v>269.0348115632177</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3205536389750143</v>
+        <v>-0.3119622730793603</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9524849534883089</v>
+        <v>0.9523103791293794</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3365445698654272</v>
+        <v>-0.3275846613837836</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133167467411397</v>
+        <v>0.7131588368540057</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372000199797376</v>
+        <v>1.371493646499388</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.131476340790977</v>
+        <v>6.143794484196141</v>
       </c>
       <c r="E12" t="n">
-        <v>120.7893934588445</v>
+        <v>117.6521225508291</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2998072411508066</v>
+        <v>-0.2966755032202015</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6539910759371788</v>
+        <v>0.6539482990777487</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4584271134299172</v>
+        <v>-0.4536681319281625</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887465302185999</v>
+        <v>0.7886589376476794</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041652629588779</v>
+        <v>1.041505717278893</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.721409619562107</v>
+        <v>4.733214234571719</v>
       </c>
       <c r="E13" t="n">
-        <v>312.3075985215337</v>
+        <v>297.4861707117671</v>
       </c>
       <c r="F13" t="n">
-        <v>1.706073730605743</v>
+        <v>1.717957675095166</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8570839902350758</v>
+        <v>0.8569715824885897</v>
       </c>
       <c r="H13" t="n">
-        <v>1.990556059900048</v>
+        <v>2.00468453120269</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020772233752364</v>
+        <v>0.6020237882255177</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042051568386589</v>
+        <v>1.041859335120819</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.377069529676555</v>
+        <v>4.394162782024238</v>
       </c>
       <c r="E14" t="n">
-        <v>127.3007907711024</v>
+        <v>127.1767454067303</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4283705522414626</v>
+        <v>-0.4253635445125251</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445727735072812</v>
+        <v>0.8445167267341752</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5072038380571471</v>
+        <v>-0.5036768734675576</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601253955793115</v>
+        <v>0.7600478728097902</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296390828854617</v>
+        <v>1.296218507365802</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.017797693880548</v>
+        <v>4.025364808105613</v>
       </c>
       <c r="E15" t="n">
-        <v>154.0514650858856</v>
+        <v>243.4171522225695</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4525420506079885</v>
+        <v>-0.06106778720864592</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9554588711311052</v>
+        <v>0.7897280534541088</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4736384414666155</v>
+        <v>-0.07732761542602916</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>274</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5138466983622132</v>
+        <v>0.7130664150288702</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9914234752744348</v>
+        <v>1.137199243279717</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.986851566780058</v>
+        <v>4.010286517000714</v>
       </c>
       <c r="E16" t="n">
-        <v>235.7337887749929</v>
+        <v>155.7933925577842</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07422994909455738</v>
+        <v>0.4472899594315474</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7899539354291416</v>
+        <v>0.9555376951109912</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.09396744008146758</v>
+        <v>0.4681028929785884</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7132583673894424</v>
+        <v>0.5138707267724529</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13779042009825</v>
+        <v>0.9915867546919885</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.706266990702266</v>
+        <v>3.719014812240473</v>
       </c>
       <c r="E17" t="n">
-        <v>158.5327574149704</v>
+        <v>160.1922682446455</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1010667430402775</v>
+        <v>-0.09547104679266649</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7511338555365111</v>
+        <v>0.7510210287984884</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.134552240316859</v>
+        <v>-0.1271216692099882</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.720904367524163</v>
+        <v>0.7208264312098572</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093474411351907</v>
+        <v>1.093230689590976</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.03833502816753</v>
+        <v>3.054777705315121</v>
       </c>
       <c r="E18" t="n">
-        <v>71.05109211383257</v>
+        <v>70.88897372181329</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4793177678038928</v>
+        <v>-0.4754401488658833</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407819960238377</v>
+        <v>0.7407203666951909</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6470429497161656</v>
+        <v>-0.6418618553545573</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644357156981753</v>
+        <v>0.7642903705291106</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14352330283499</v>
+        <v>1.143251259010671</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.954559323246497</v>
+        <v>2.964700827948212</v>
       </c>
       <c r="E19" t="n">
-        <v>67.91917420880405</v>
+        <v>71.46292468068546</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1073395335216012</v>
+        <v>0.1137377774552892</v>
       </c>
       <c r="G19" t="n">
-        <v>0.478200299652031</v>
+        <v>0.4782413030510369</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2244656341698411</v>
+        <v>0.2378250827138437</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7169692018324033</v>
+        <v>0.7166733187606185</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6923472555774952</v>
+        <v>0.6921453916698768</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.58550503995294</v>
+        <v>2.587961843583622</v>
       </c>
       <c r="E20" t="n">
-        <v>131.9305548313361</v>
+        <v>130.2998130350362</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3182164331458633</v>
+        <v>-0.3167181418101322</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7734016066593395</v>
+        <v>0.7733581574829428</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4114504423133791</v>
+        <v>-0.4095361751157552</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322305982284053</v>
+        <v>0.7322032901762526</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143580058564259</v>
+        <v>1.143513671694894</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>562.5512009818385</v>
+        <v>561.8975865716133</v>
       </c>
       <c r="E2" t="n">
-        <v>13318.23541538972</v>
+        <v>13396.87625185097</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5853992362708655</v>
+        <v>0.5819945055735127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.49518899634524</v>
+        <v>0.4952388165319314</v>
       </c>
       <c r="H2" t="n">
-        <v>1.182173353187218</v>
+        <v>1.175179501576867</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.1536773916811</v>
+        <v>221.8547546942381</v>
       </c>
       <c r="E3" t="n">
-        <v>5678.414804681795</v>
+        <v>5766.93250437128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2295869514238134</v>
+        <v>0.2262615828673029</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5937533092906018</v>
+        <v>0.5938093871662277</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3866706051678546</v>
+        <v>0.3810340283555748</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907252105054521</v>
+        <v>0.8907470412092572</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068018565253936</v>
+        <v>1.068038160588116</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.73248978644512</v>
+        <v>37.63226918219641</v>
       </c>
       <c r="E4" t="n">
-        <v>687.9456795702848</v>
+        <v>726.9199070066966</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3126664674597445</v>
+        <v>-0.3171328569417705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5578740799402215</v>
+        <v>0.5576618734549804</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5604606464119071</v>
+        <v>-0.5686830533652618</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7342373026236262</v>
+        <v>0.7345837394016083</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8271830809692885</v>
+        <v>0.8271753559080178</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.41429103030152</v>
+        <v>36.36999800788707</v>
       </c>
       <c r="E5" t="n">
-        <v>1676.688113474105</v>
+        <v>1649.22139357071</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7022814320858282</v>
+        <v>0.6950749472035231</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100676564083331</v>
+        <v>1.100724012579259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6380452305448188</v>
+        <v>0.6314706858940933</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4738034228363468</v>
+        <v>0.4738732142255607</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053141986892708</v>
+        <v>1.053236556594829</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.79384657532092</v>
+        <v>10.79757959756435</v>
       </c>
       <c r="E6" t="n">
-        <v>411.7530853584049</v>
+        <v>409.4476419206379</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4859545432093765</v>
+        <v>-0.4869328059377676</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8102284294768416</v>
+        <v>0.8102539361404216</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5997747370123184</v>
+        <v>-0.6009632094565713</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666857300379516</v>
+        <v>0.6667102891464589</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090831452213192</v>
+        <v>1.090796234085997</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.67671581809037</v>
+        <v>10.66624059542535</v>
       </c>
       <c r="E7" t="n">
-        <v>240.8327722743505</v>
+        <v>241.9674011122818</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3145317418352761</v>
+        <v>-0.3160262988633702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100122738635899</v>
+        <v>0.7100294407142714</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4429947951797029</v>
+        <v>-0.4450890072184272</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501136948627734</v>
+        <v>0.7501256310105169</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075528604384459</v>
+        <v>1.075463522794151</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.53127140435288</v>
+        <v>9.473767903146225</v>
       </c>
       <c r="E8" t="n">
-        <v>428.7338714297467</v>
+        <v>427.3975862230747</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3479259440856937</v>
+        <v>-0.3549039507138018</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164145838159876</v>
+        <v>1.164231093311275</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2988680049190811</v>
+        <v>-0.3048397803089019</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7371063687134948</v>
+        <v>0.7372270517594723</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732872333093397</v>
+        <v>1.733108609093119</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.997349618932689</v>
+        <v>7.000417793138699</v>
       </c>
       <c r="E9" t="n">
-        <v>252.6008603181862</v>
+        <v>236.1744309320389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3250474553394318</v>
+        <v>0.3236921043915464</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812744342457686</v>
+        <v>0.4812718640192756</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6753889926624326</v>
+        <v>0.6725764138553133</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6729696845442534</v>
+        <v>0.6729447042983036</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6540595743928475</v>
+        <v>0.6539660087380545</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.659136076531319</v>
+        <v>6.652856075131188</v>
       </c>
       <c r="E10" t="n">
-        <v>578.6940957874275</v>
+        <v>584.6617675363536</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9469454310732499</v>
+        <v>0.9418006106013954</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8167491268500712</v>
+        <v>0.8168143480567647</v>
       </c>
       <c r="H10" t="n">
-        <v>1.159407950303299</v>
+        <v>1.153016732433727</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6639101369463956</v>
+        <v>0.6639726666506808</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095032459646641</v>
+        <v>1.095112868243474</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.345287972850897</v>
+        <v>6.338847448689619</v>
       </c>
       <c r="E11" t="n">
-        <v>269.0348115632177</v>
+        <v>269.8696132194498</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3119622730793603</v>
+        <v>-0.3131720589791556</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9523103791293794</v>
+        <v>0.9523277105186659</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3275846613837836</v>
+        <v>-0.3288490458905084</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7131588368540057</v>
+        <v>0.7131596897653346</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371493646499388</v>
+        <v>1.37138227440343</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.143794484196141</v>
+        <v>6.14796691991856</v>
       </c>
       <c r="E12" t="n">
-        <v>117.6521225508291</v>
+        <v>122.0421044339665</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2966755032202015</v>
+        <v>-0.2972284159880094</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6539482990777487</v>
+        <v>0.653954231728592</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4536681319281625</v>
+        <v>-0.4545095078020184</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7886589376476794</v>
+        <v>0.7886330377761217</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041505717278893</v>
+        <v>1.041376190877431</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.733214234571719</v>
+        <v>4.728475008595561</v>
       </c>
       <c r="E13" t="n">
-        <v>297.4861707117671</v>
+        <v>274.1078655851084</v>
       </c>
       <c r="F13" t="n">
-        <v>1.717957675095166</v>
+        <v>1.712014079964409</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8569715824885897</v>
+        <v>0.8570257925083599</v>
       </c>
       <c r="H13" t="n">
-        <v>2.00468453120269</v>
+        <v>1.99762258607603</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020237882255177</v>
+        <v>0.6020922334396298</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041859335120819</v>
+        <v>1.041938871311103</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.394162782024238</v>
+        <v>4.401981762155755</v>
       </c>
       <c r="E14" t="n">
-        <v>127.1767454067303</v>
+        <v>127.6664807809332</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4253635445125251</v>
+        <v>-0.4247616712537874</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445167267341752</v>
+        <v>0.8445083567735197</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5036768734675576</v>
+        <v>-0.5029691747238684</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600478728097902</v>
+        <v>0.759984756587185</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296218507365802</v>
+        <v>1.295967635277201</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.025364808105613</v>
+        <v>4.022357043789518</v>
       </c>
       <c r="E15" t="n">
-        <v>243.4171522225695</v>
+        <v>244.0416010400716</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06106778720864592</v>
+        <v>-0.06390406040553509</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7897280534541088</v>
+        <v>0.7897612737590749</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07732761542602916</v>
+        <v>-0.08091566721341886</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7130664150288702</v>
+        <v>0.7131012056117434</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137199243279717</v>
+        <v>1.137188155821284</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.010286517000714</v>
+        <v>4.002308273426644</v>
       </c>
       <c r="E16" t="n">
-        <v>155.7933925577842</v>
+        <v>156.6054852978521</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4472899594315474</v>
+        <v>0.4486025374842897</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9555376951109912</v>
+        <v>0.9555170730366273</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4681028929785884</v>
+        <v>0.4694866791428788</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5138707267724529</v>
+        <v>0.5139081502259238</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9915867546919885</v>
+        <v>0.9915378098838518</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.719014812240473</v>
+        <v>3.717345589996019</v>
       </c>
       <c r="E17" t="n">
-        <v>160.1922682446455</v>
+        <v>159.2694119086579</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.09547104679266649</v>
+        <v>-0.09640426382511669</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7510210287984884</v>
+        <v>0.7510372687108583</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1271216692099882</v>
+        <v>-0.1283614912886984</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7208264312098572</v>
+        <v>0.7208385301557343</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093230689590976</v>
+        <v>1.093162698071358</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.054777705315121</v>
+        <v>3.050431172746846</v>
       </c>
       <c r="E18" t="n">
-        <v>70.88897372181329</v>
+        <v>71.87235701255025</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4754401488658833</v>
+        <v>-0.476944566698416</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407203666951909</v>
+        <v>0.7407378276366769</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6418618553545573</v>
+        <v>-0.6438776972145557</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642903705291106</v>
+        <v>0.7643119992403942</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143251259010671</v>
+        <v>1.143195547389955</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.964700827948212</v>
+        <v>2.983718182597897</v>
       </c>
       <c r="E19" t="n">
-        <v>71.46292468068546</v>
+        <v>82.02396619489932</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1137377774552892</v>
+        <v>0.1201451986104647</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4782413030510369</v>
+        <v>0.478334100591754</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2378250827138437</v>
+        <v>0.2511742283517552</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7166733187606185</v>
+        <v>0.7161101781114116</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6921453916698768</v>
+        <v>0.6916661346747183</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.587961843583622</v>
+        <v>2.588616212143596</v>
       </c>
       <c r="E20" t="n">
-        <v>130.2998130350362</v>
+        <v>124.5834375998267</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3167181418101322</v>
+        <v>-0.3177170938181112</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7733581574829428</v>
+        <v>0.7733866274947238</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4095361751157552</v>
+        <v>-0.4108127584870592</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322032901762526</v>
+        <v>0.732231220474423</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143513671694894</v>
+        <v>1.143484345824791</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>561.8975865716133</v>
+        <v>560.2979926553755</v>
       </c>
       <c r="E2" t="n">
-        <v>13396.87625185097</v>
+        <v>13643.97213060455</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5819945055735127</v>
+        <v>0.5750157855826339</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4952388165319314</v>
+        <v>0.4953621883208197</v>
       </c>
       <c r="H2" t="n">
-        <v>1.175179501576867</v>
+        <v>1.160798702726634</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.8547546942381</v>
+        <v>219.6935479849474</v>
       </c>
       <c r="E3" t="n">
-        <v>5766.93250437128</v>
+        <v>5811.524225295615</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2262615828673029</v>
+        <v>0.2229117426402782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5938093871662277</v>
+        <v>0.5938749530011634</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3810340283555748</v>
+        <v>0.3753513117766419</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907470412092572</v>
+        <v>0.8907693929450966</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068038160588116</v>
+        <v>1.067916857286522</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.63226918219641</v>
+        <v>37.67749110086481</v>
       </c>
       <c r="E4" t="n">
-        <v>726.9199070066966</v>
+        <v>743.9722975202254</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3171328569417705</v>
+        <v>-0.31601694033773</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5576618734549804</v>
+        <v>0.5577094569228218</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5686830533652618</v>
+        <v>-0.5666336412535707</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7345837394016083</v>
+        <v>0.7340012357515626</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8271753559080178</v>
+        <v>0.8263840886994864</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.36999800788707</v>
+        <v>36.19142860852866</v>
       </c>
       <c r="E5" t="n">
-        <v>1649.22139357071</v>
+        <v>1665.745994416955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6950749472035231</v>
+        <v>0.684606412991549</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100724012579259</v>
+        <v>1.100814215504498</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6314706858940933</v>
+        <v>0.6219091317582566</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4738732142255607</v>
+        <v>0.4740033138940099</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053236556594829</v>
+        <v>1.05334964685038</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.79757959756435</v>
+        <v>10.76835987819145</v>
       </c>
       <c r="E6" t="n">
-        <v>409.4476419206379</v>
+        <v>402.0272419748123</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4869328059377676</v>
+        <v>-0.4879106038522999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8102539361404216</v>
+        <v>0.8102826784802928</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6009632094565713</v>
+        <v>-0.6021486288802194</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667102891464589</v>
+        <v>0.6667208196623994</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090796234085997</v>
+        <v>1.090580476854534</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.66624059542535</v>
+        <v>10.64003820419393</v>
       </c>
       <c r="E7" t="n">
-        <v>241.9674011122818</v>
+        <v>250.1994863789342</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3160262988633702</v>
+        <v>-0.3196099138790252</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100294407142714</v>
+        <v>0.7100906642391748</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4450890072184272</v>
+        <v>-0.4500973326011412</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501256310105169</v>
+        <v>0.7501849676655534</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075463522794151</v>
+        <v>1.075373443010704</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.473767903146225</v>
+        <v>9.428253183715139</v>
       </c>
       <c r="E8" t="n">
-        <v>427.3975862230747</v>
+        <v>429.6106925482205</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3549039507138018</v>
+        <v>-0.3600336359551259</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164231093311275</v>
+        <v>1.164340199967889</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3048397803089019</v>
+        <v>-0.3092168731828165</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372270517594723</v>
+        <v>0.737287445708119</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733108609093119</v>
+        <v>1.732981305819068</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.000417793138699</v>
+        <v>6.995229316918556</v>
       </c>
       <c r="E9" t="n">
-        <v>236.1744309320389</v>
+        <v>236.9957778642492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3236921043915464</v>
+        <v>0.3230145586201141</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812718640192756</v>
+        <v>0.4812711859142165</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6725764138553133</v>
+        <v>0.6711695361660179</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6729447042983036</v>
+        <v>0.6727965128226233</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6539660087380545</v>
+        <v>0.6536582388387442</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.652856075131188</v>
+        <v>6.617123977751204</v>
       </c>
       <c r="E10" t="n">
-        <v>584.6617675363536</v>
+        <v>591.126859735987</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9418006106013954</v>
+        <v>0.9263865446884376</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8168143480567647</v>
+        <v>0.8170466914115947</v>
       </c>
       <c r="H10" t="n">
-        <v>1.153016732433727</v>
+        <v>1.133823261786837</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6639726666506808</v>
+        <v>0.6641507625136448</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095112868243474</v>
+        <v>1.09544530427264</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.338847448689619</v>
+        <v>6.329228446021079</v>
       </c>
       <c r="E11" t="n">
-        <v>269.8696132194498</v>
+        <v>274.0761431958551</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3131720589791556</v>
+        <v>-0.3161270768371642</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9523277105186659</v>
+        <v>0.952380021995606</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3288490458905084</v>
+        <v>-0.3319337549466391</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7131596897653346</v>
+        <v>0.7131775277066523</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37138227440343</v>
+        <v>1.371150333105645</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.14796691991856</v>
+        <v>6.233160256248525</v>
       </c>
       <c r="E12" t="n">
-        <v>122.0421044339665</v>
+        <v>125.1481778085751</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2972284159880094</v>
+        <v>-0.2996231177591734</v>
       </c>
       <c r="G12" t="n">
-        <v>0.653954231728592</v>
+        <v>0.6539879439848058</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4545095078020184</v>
+        <v>-0.4581477694122976</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7886330377761217</v>
+        <v>0.7886300847154705</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041376190877431</v>
+        <v>1.041166604612961</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.728475008595561</v>
+        <v>4.695123029418943</v>
       </c>
       <c r="E13" t="n">
-        <v>274.1078655851084</v>
+        <v>274.1849241876187</v>
       </c>
       <c r="F13" t="n">
-        <v>1.712014079964409</v>
+        <v>1.671979889636791</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8570257925083599</v>
+        <v>0.8574959695852806</v>
       </c>
       <c r="H13" t="n">
-        <v>1.99762258607603</v>
+        <v>1.949839939708903</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6020922334396298</v>
+        <v>0.6023758404909098</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041938871311103</v>
+        <v>1.042741790905463</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.401981762155755</v>
+        <v>4.377633252555308</v>
       </c>
       <c r="E14" t="n">
-        <v>127.6664807809332</v>
+        <v>128.2175198908774</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4247616712537874</v>
+        <v>-0.4301728670452134</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445083567735197</v>
+        <v>0.8446177577331461</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5029691747238684</v>
+        <v>-0.5093107066559273</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.759984756587185</v>
+        <v>0.7601130179453295</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295967635277201</v>
+        <v>1.296031404853546</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.022357043789518</v>
+        <v>4.016450358464581</v>
       </c>
       <c r="E15" t="n">
-        <v>244.0416010400716</v>
+        <v>156.6958958554793</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06390406040553509</v>
+        <v>0.4499154121210351</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7897612737590749</v>
+        <v>0.9554970616564723</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08091566721341886</v>
+        <v>0.4708705344850053</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>274</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7131012056117434</v>
+        <v>0.5139632453197939</v>
       </c>
       <c r="N15" t="n">
-        <v>1.137188155821284</v>
+        <v>0.9913763752683412</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.002308273426644</v>
+        <v>4.003876032372235</v>
       </c>
       <c r="E16" t="n">
-        <v>156.6054852978521</v>
+        <v>249.0030739566207</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4486025374842897</v>
+        <v>-0.07006972062527095</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9555170730366273</v>
+        <v>0.7898627479032041</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4694866791428788</v>
+        <v>-0.08871126130619574</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5139081502259238</v>
+        <v>0.7132025727271073</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9915378098838518</v>
+        <v>1.137212643975619</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.717345589996019</v>
+        <v>3.709836732611348</v>
       </c>
       <c r="E17" t="n">
-        <v>159.2694119086579</v>
+        <v>156.6290561023081</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.09640426382511669</v>
+        <v>-0.1025574654263711</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7510372687108583</v>
+        <v>0.7511701785705581</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1283614912886984</v>
+        <v>-0.1365302675107966</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7208385301557343</v>
+        <v>0.7209587286542185</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093162698071358</v>
+        <v>1.09326611863732</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.050431172746846</v>
+        <v>3.038476703702761</v>
       </c>
       <c r="E18" t="n">
-        <v>71.87235701255025</v>
+        <v>73.2683676070121</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.476944566698416</v>
+        <v>-0.4800292031399844</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407378276366769</v>
+        <v>0.7407992094110758</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6438776972145557</v>
+        <v>-0.647988276771516</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643119992403942</v>
+        <v>0.7643742118760378</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143195547389955</v>
+        <v>1.143098575552267</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.983718182597897</v>
+        <v>2.917169754974188</v>
       </c>
       <c r="E19" t="n">
-        <v>82.02396619489932</v>
+        <v>86.45511860633935</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1201451986104647</v>
+        <v>0.08456398278064614</v>
       </c>
       <c r="G19" t="n">
-        <v>0.478334100591754</v>
+        <v>0.4784767062055527</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2511742283517552</v>
+        <v>0.1767358403949504</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7161101781114116</v>
+        <v>0.7176606975554777</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6916661346747183</v>
+        <v>0.6931976942033631</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.588616212143596</v>
+        <v>2.5874702185677</v>
       </c>
       <c r="E20" t="n">
-        <v>124.5834375998267</v>
+        <v>124.5934698687745</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3177170938181112</v>
+        <v>-0.3187156813115255</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7733866274947238</v>
+        <v>0.7734170818916573</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4108127584870592</v>
+        <v>-0.4120877192575018</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.732231220474423</v>
+        <v>0.7322590089924949</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143484345824791</v>
+        <v>1.143287960358134</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>560.2979926553755</v>
+        <v>561.1042797703301</v>
       </c>
       <c r="E2" t="n">
-        <v>13643.97213060455</v>
+        <v>13924.22269202346</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5750157855826339</v>
+        <v>0.5780336113905689</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4953621883208197</v>
+        <v>0.4953053290146321</v>
       </c>
       <c r="H2" t="n">
-        <v>1.160798702726634</v>
+        <v>1.167024817884592</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>219.6935479849474</v>
+        <v>222.0406602715285</v>
       </c>
       <c r="E3" t="n">
-        <v>5811.524225295615</v>
+        <v>5875.18266328831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2229117426402782</v>
+        <v>0.2271350547155855</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5938749530011634</v>
+        <v>0.5937937886690664</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3753513117766419</v>
+        <v>0.3825150398165794</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907693929450966</v>
+        <v>0.8907299438146637</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067916857286522</v>
+        <v>1.067846189078796</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.67749110086481</v>
+        <v>37.62210168502152</v>
       </c>
       <c r="E4" t="n">
-        <v>743.9722975202254</v>
+        <v>742.630846893091</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.31601694033773</v>
+        <v>-0.3171328569417705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5577094569228218</v>
+        <v>0.5576618734549804</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5666336412535707</v>
+        <v>-0.5686830533652618</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7340012357515626</v>
+        <v>0.7343470800330553</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8263840886994864</v>
+        <v>0.8267978243483229</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.19142860852866</v>
+        <v>36.44552290637217</v>
       </c>
       <c r="E5" t="n">
-        <v>1665.745994416955</v>
+        <v>1649.687033914329</v>
       </c>
       <c r="F5" t="n">
-        <v>0.684606412991549</v>
+        <v>0.7183595810745385</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100814215504498</v>
+        <v>1.100613547400237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6219091317582566</v>
+        <v>0.652690113411177</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4740033138940099</v>
+        <v>0.4735671555198527</v>
       </c>
       <c r="N5" t="n">
-        <v>1.05334964685038</v>
+        <v>1.052309346248821</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.76835987819145</v>
+        <v>10.80798262686108</v>
       </c>
       <c r="E6" t="n">
-        <v>402.0272419748123</v>
+        <v>390.0597681457504</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4879106038522999</v>
+        <v>-0.4859545432093765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8102826784802928</v>
+        <v>0.8102284294768416</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6021486288802194</v>
+        <v>-0.5997747370123184</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667208196623994</v>
+        <v>0.6666471659735762</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090580476854534</v>
+        <v>1.090512164237186</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.64003820419393</v>
+        <v>10.67457537446974</v>
       </c>
       <c r="E7" t="n">
-        <v>250.1994863789342</v>
+        <v>248.8167000738066</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3196099138790252</v>
+        <v>-0.3148307182991567</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100906642391748</v>
+        <v>0.7100153145882296</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4500973326011412</v>
+        <v>-0.443413982530421</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501849676655534</v>
+        <v>0.750014895867907</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075373443010704</v>
+        <v>1.075138971944675</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.428253183715139</v>
+        <v>9.444742855827254</v>
       </c>
       <c r="E8" t="n">
-        <v>429.6106925482205</v>
+        <v>413.4928807272234</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3600336359551259</v>
+        <v>-0.3589352775551111</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164340199967889</v>
+        <v>1.16431351432068</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3092168731828165</v>
+        <v>-0.3082806075342449</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737287445708119</v>
+        <v>0.7372850157118338</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732981305819068</v>
+        <v>1.733134810819012</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.995229316918556</v>
+        <v>6.98826389253444</v>
       </c>
       <c r="E9" t="n">
-        <v>236.9957778642492</v>
+        <v>229.6195218748356</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3230145586201141</v>
+        <v>0.3216597265932748</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812711859142165</v>
+        <v>0.4812710437290257</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6711695361660179</v>
+        <v>0.6683546221708316</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6727965128226233</v>
+        <v>0.6729386520893086</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6536582388387442</v>
+        <v>0.6538711951695109</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.617123977751204</v>
+        <v>6.882445692049316</v>
       </c>
       <c r="E10" t="n">
-        <v>591.126859735987</v>
+        <v>639.7066419398229</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9263865446884376</v>
+        <v>1.034055486621409</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8170466914115947</v>
+        <v>0.8165698561810264</v>
       </c>
       <c r="H10" t="n">
-        <v>1.133823261786837</v>
+        <v>1.266340508156314</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6641507625136448</v>
+        <v>0.6625851076408008</v>
       </c>
       <c r="N10" t="n">
-        <v>1.09544530427264</v>
+        <v>1.092350504546974</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.329228446021079</v>
+        <v>6.399076336283536</v>
       </c>
       <c r="E11" t="n">
-        <v>274.0761431958551</v>
+        <v>124.3874271222786</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3161270768371642</v>
+        <v>-0.2940938111636358</v>
       </c>
       <c r="G11" t="n">
-        <v>0.952380021995606</v>
+        <v>0.6539297727370489</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3319337549466391</v>
+        <v>-0.4497330193924257</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J11" t="n">
         <v>274</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7131775277066523</v>
+        <v>0.7884022406020975</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371150333105645</v>
+        <v>1.04089269349872</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.233160256248525</v>
+        <v>6.34459577374021</v>
       </c>
       <c r="E12" t="n">
-        <v>125.1481778085751</v>
+        <v>272.1619446071575</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2996231177591734</v>
+        <v>-0.3143813138391396</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6539879439848058</v>
+        <v>0.9523474044854833</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4581477694122976</v>
+        <v>-0.3301120078223846</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J12" t="n">
         <v>274</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7886300847154705</v>
+        <v>0.7131548222172224</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041166604612961</v>
+        <v>1.371217114271779</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.695123029418943</v>
+        <v>4.719925240535567</v>
       </c>
       <c r="E13" t="n">
-        <v>274.1849241876187</v>
+        <v>254.5262280779356</v>
       </c>
       <c r="F13" t="n">
-        <v>1.671979889636791</v>
+        <v>1.700136630589523</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8574959695852806</v>
+        <v>0.8571461748564762</v>
       </c>
       <c r="H13" t="n">
-        <v>1.949839939708903</v>
+        <v>1.983485058279821</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6023758404909098</v>
+        <v>0.6022015275067224</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042741790905463</v>
+        <v>1.04213442811528</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.377633252555308</v>
+        <v>4.39889978893075</v>
       </c>
       <c r="E14" t="n">
-        <v>128.2175198908774</v>
+        <v>125.8412988115033</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4301728670452134</v>
+        <v>-0.4259652606437964</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8446177577331461</v>
+        <v>0.8445260432044319</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5093107066559273</v>
+        <v>-0.5043838068362377</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601130179453295</v>
+        <v>0.7599754183434132</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296031404853546</v>
+        <v>1.295804820559957</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.016450358464581</v>
+        <v>4.030666492094319</v>
       </c>
       <c r="E15" t="n">
-        <v>156.6958958554793</v>
+        <v>154.1429948754612</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4499154121210351</v>
+        <v>0.468326723214691</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9554970616564723</v>
+        <v>0.9552810445867482</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4708705344850053</v>
+        <v>0.4902502000521614</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139632453197939</v>
+        <v>0.513680332751022</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9913763752683412</v>
+        <v>0.9907203821737368</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.003876032372235</v>
+        <v>4.007937522416052</v>
       </c>
       <c r="E16" t="n">
-        <v>249.0030739566207</v>
+        <v>241.328190099073</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.07006972062527095</v>
+        <v>-0.06857090065131088</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7898627479032041</v>
+        <v>0.7898343862970906</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08871126130619574</v>
+        <v>-0.08681680848663181</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7132025727271073</v>
+        <v>0.7131814266963377</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137212643975619</v>
+        <v>1.137268633054713</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.709836732611348</v>
+        <v>3.723369041809468</v>
       </c>
       <c r="E17" t="n">
-        <v>156.6290561023081</v>
+        <v>152.3774582711002</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1025574654263711</v>
+        <v>-0.09603100583281676</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7511701785705581</v>
+        <v>0.7510306496321552</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1365302675107966</v>
+        <v>-0.127865628226826</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7209587286542185</v>
+        <v>0.7208146077317666</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09326611863732</v>
+        <v>1.092969995267593</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.038476703702761</v>
+        <v>3.048752238795633</v>
       </c>
       <c r="E18" t="n">
-        <v>73.2683676070121</v>
+        <v>74.77584650358276</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4800292031399844</v>
+        <v>-0.477261148928792</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407992094110758</v>
+        <v>0.7407425424851847</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.647988276771516</v>
+        <v>-0.64430098388515</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643742118760378</v>
+        <v>0.7642655095153512</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143098575552267</v>
+        <v>1.142979781336882</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.917169754974188</v>
+        <v>2.92009126696524</v>
       </c>
       <c r="E19" t="n">
-        <v>86.45511860633935</v>
+        <v>89.86236116667017</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08456398278064614</v>
+        <v>0.08729080989429905</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4784767062055527</v>
+        <v>0.4784086703112819</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1767358403949504</v>
+        <v>0.1824607606661943</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7176606975554777</v>
+        <v>0.7175844784432391</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6931976942033631</v>
+        <v>0.6931050728870785</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.5874702185677</v>
+        <v>2.596836451999467</v>
       </c>
       <c r="E20" t="n">
-        <v>124.5934698687745</v>
+        <v>124.3950120426964</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3187156813115255</v>
+        <v>-0.3142191687918265</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7734170818916573</v>
+        <v>0.7732956655392681</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4120877192575018</v>
+        <v>-0.4063376827189398</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322590089924949</v>
+        <v>0.7321342740749504</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143287960358134</v>
+        <v>1.143044961501257</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>561.1042797703301</v>
+        <v>562.4986142959981</v>
       </c>
       <c r="E2" t="n">
-        <v>13924.22269202346</v>
+        <v>15342.06189168145</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5780336113905689</v>
+        <v>0.5827037347069499</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4953053290146321</v>
+        <v>0.4952278784391171</v>
       </c>
       <c r="H2" t="n">
-        <v>1.167024817884592</v>
+        <v>1.176637584587409</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.0406602715285</v>
+        <v>220.132186111237</v>
       </c>
       <c r="E3" t="n">
-        <v>5875.18266328831</v>
+        <v>6536.294022634524</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2271350547155855</v>
+        <v>0.2258159937113309</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5937937886690664</v>
+        <v>0.5938175830432354</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3825150398165794</v>
+        <v>0.3802783887840677</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907299438146637</v>
+        <v>0.89074887885078</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067846189078796</v>
+        <v>1.068078695417527</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.62210168502152</v>
+        <v>37.64796333723294</v>
       </c>
       <c r="E4" t="n">
-        <v>742.630846893091</v>
+        <v>775.5075961506129</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3171328569417705</v>
+        <v>-0.3163889630120496</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5576618734549804</v>
+        <v>0.5576931905951811</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5686830533652618</v>
+        <v>-0.5673172424328744</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7343470800330553</v>
+        <v>0.7345351754373841</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8267978243483229</v>
+        <v>0.8271853896537597</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.44552290637217</v>
+        <v>36.60108594232301</v>
       </c>
       <c r="E5" t="n">
-        <v>1649.687033914329</v>
+        <v>1730.086747222041</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7183595810745385</v>
+        <v>0.7127771798192157</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100613547400237</v>
+        <v>1.10062873859089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.652690113411177</v>
+        <v>0.6476090936274919</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4735671555198527</v>
+        <v>0.473685306277342</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052309346248821</v>
+        <v>1.052751034090187</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.80798262686108</v>
+        <v>10.78731395136936</v>
       </c>
       <c r="E6" t="n">
-        <v>390.0597681457504</v>
+        <v>394.3065937772385</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4859545432093765</v>
+        <v>-0.4877328570062611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8102284294768416</v>
+        <v>0.8102772119451845</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5997747370123184</v>
+        <v>-0.6019333258001786</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666471659735762</v>
+        <v>0.6667392092174276</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090512164237186</v>
+        <v>1.090898980166463</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.67457537446974</v>
+        <v>10.67492227376213</v>
       </c>
       <c r="E7" t="n">
-        <v>248.8167000738066</v>
+        <v>261.4649058761167</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3148307182991567</v>
+        <v>-0.3175200421287203</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100153145882296</v>
+        <v>0.7100515154017487</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.443413982530421</v>
+        <v>-0.4471788810267756</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.750014895867907</v>
+        <v>0.75018514509517</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075138971944675</v>
+        <v>1.075606043798667</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.444742855827254</v>
+        <v>9.438118389872537</v>
       </c>
       <c r="E8" t="n">
-        <v>413.4928807272234</v>
+        <v>427.6395312367392</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3589352775551111</v>
+        <v>-0.3593014491945443</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16431351432068</v>
+        <v>1.164322209211054</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3082806075342449</v>
+        <v>-0.3085927987562889</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372850157118338</v>
+        <v>0.7373162578633264</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733134810819012</v>
+        <v>1.73349226006507</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.98826389253444</v>
+        <v>7.000808650928733</v>
       </c>
       <c r="E9" t="n">
-        <v>229.6195218748356</v>
+        <v>211.6975194666382</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3216597265932748</v>
+        <v>0.3259512147186996</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812710437290257</v>
+        <v>0.4812770469908075</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6683546221708316</v>
+        <v>0.6772631621572539</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6729386520893086</v>
+        <v>0.6728674049847231</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6538711951695109</v>
+        <v>0.6539123740531247</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.882445692049316</v>
+        <v>6.819305465429697</v>
       </c>
       <c r="E10" t="n">
-        <v>639.7066419398229</v>
+        <v>744.381568974489</v>
       </c>
       <c r="F10" t="n">
-        <v>1.034055486621409</v>
+        <v>1.000594225541924</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8165698561810264</v>
+        <v>0.8164335504828735</v>
       </c>
       <c r="H10" t="n">
-        <v>1.266340508156314</v>
+        <v>1.225567255228708</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6625851076408008</v>
+        <v>0.663391329921974</v>
       </c>
       <c r="N10" t="n">
-        <v>1.092350504546974</v>
+        <v>1.093668112051446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.399076336283536</v>
+        <v>6.376134429579857</v>
       </c>
       <c r="E11" t="n">
-        <v>124.3874271222786</v>
+        <v>286.441553619517</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2940938111636358</v>
+        <v>-0.3096756747045648</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6539297727370489</v>
+        <v>0.9522840885480059</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4497330193924257</v>
+        <v>-0.3251925328047247</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J11" t="n">
         <v>274</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7884022406020975</v>
+        <v>0.7130698873017333</v>
       </c>
       <c r="N11" t="n">
-        <v>1.04089269349872</v>
+        <v>1.371177062649233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.34459577374021</v>
+        <v>6.168602846198762</v>
       </c>
       <c r="E12" t="n">
-        <v>272.1619446071575</v>
+        <v>125.4680503794765</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3143813138391396</v>
+        <v>-0.2942782959287031</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9523474044854833</v>
+        <v>0.6539305957286048</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3301120078223846</v>
+        <v>-0.4500145701254739</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J12" t="n">
         <v>274</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7131548222172224</v>
+        <v>0.7885165094171898</v>
       </c>
       <c r="N12" t="n">
-        <v>1.371217114271779</v>
+        <v>1.041207680735233</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.719925240535567</v>
+        <v>4.700807886722307</v>
       </c>
       <c r="E13" t="n">
-        <v>254.5262280779356</v>
+        <v>265.0684970996963</v>
       </c>
       <c r="F13" t="n">
-        <v>1.700136630589523</v>
+        <v>1.682344862446713</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8571461748564762</v>
+        <v>0.8573566411355266</v>
       </c>
       <c r="H13" t="n">
-        <v>1.983485058279821</v>
+        <v>1.962246259874456</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6022015275067224</v>
+        <v>0.6021548600536438</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04213442811528</v>
+        <v>1.042472547963581</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.39889978893075</v>
+        <v>4.391903735294353</v>
       </c>
       <c r="E14" t="n">
-        <v>125.8412988115033</v>
+        <v>130.1920954070654</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4259652606437964</v>
+        <v>-0.4277694654467058</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445260432044319</v>
+        <v>0.8445596713436649</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5043838068362377</v>
+        <v>-0.5064999904223931</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7599754183434132</v>
+        <v>0.7600982791810307</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295804820559957</v>
+        <v>1.296268608458272</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.030666492094319</v>
+        <v>4.088759103182626</v>
       </c>
       <c r="E15" t="n">
-        <v>154.1429948754612</v>
+        <v>165.4566420538629</v>
       </c>
       <c r="F15" t="n">
-        <v>0.468326723214691</v>
+        <v>0.4920831979608942</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9552810445867482</v>
+        <v>0.9551793193947071</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4902502000521614</v>
+        <v>0.5151736307196486</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.513680332751022</v>
+        <v>0.5133340121674655</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9907203821737368</v>
+        <v>0.9901018373798076</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.007937522416052</v>
+        <v>4.017327960966846</v>
       </c>
       <c r="E16" t="n">
-        <v>241.328190099073</v>
+        <v>254.1309358311068</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06857090065131088</v>
+        <v>-0.06623820741820696</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7898343862970906</v>
+        <v>0.7897949685805995</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08681680848663181</v>
+        <v>-0.08386759862151144</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131814266963377</v>
+        <v>0.7131515097039486</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137268633054713</v>
+        <v>1.137342017123703</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.723369041809468</v>
+        <v>3.747753805906791</v>
       </c>
       <c r="E17" t="n">
-        <v>152.3774582711002</v>
+        <v>148.9762854775578</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.09603100583281676</v>
+        <v>-0.08818372313789602</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7510306496321552</v>
+        <v>0.7509295735840554</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.127865628226826</v>
+        <v>-0.1174327476770032</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7208146077317666</v>
+        <v>0.7206521292143403</v>
       </c>
       <c r="N17" t="n">
-        <v>1.092969995267593</v>
+        <v>1.092747439419237</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.048752238795633</v>
+        <v>3.030591908751319</v>
       </c>
       <c r="E18" t="n">
-        <v>74.77584650358276</v>
+        <v>79.21269431821187</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.477261148928792</v>
+        <v>-0.482241005321402</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407425424851847</v>
+        <v>0.7408644568395341</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.64430098388515</v>
+        <v>-0.6509166432124466</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7642655095153512</v>
+        <v>0.7645223358192181</v>
       </c>
       <c r="N18" t="n">
-        <v>1.142979781336882</v>
+        <v>1.143730895872879</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.92009126696524</v>
+        <v>2.886883942303643</v>
       </c>
       <c r="E19" t="n">
-        <v>89.86236116667017</v>
+        <v>109.6324789639413</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08729080989429905</v>
+        <v>0.06914429185361737</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4784086703112819</v>
+        <v>0.4790415250286487</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1824607606661943</v>
+        <v>0.1443388270974677</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7175844784432391</v>
+        <v>0.7174378977233961</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6931050728870785</v>
+        <v>0.6939886860206628</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.596836451999467</v>
+        <v>2.589005534277344</v>
       </c>
       <c r="E20" t="n">
-        <v>124.3950120426964</v>
+        <v>128.6760293984987</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3142191687918265</v>
+        <v>-0.3177170938181112</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7732956655392681</v>
+        <v>0.7733866274947238</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4063376827189398</v>
+        <v>-0.4108127584870592</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321342740749504</v>
+        <v>0.7322290763126159</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143044961501257</v>
+        <v>1.143506253460265</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>562.4986142959981</v>
+        <v>566.0266199688078</v>
       </c>
       <c r="E2" t="n">
-        <v>15342.06189168145</v>
+        <v>15757.35906729426</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5827037347069499</v>
+        <v>0.5971657559780541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4952278784391171</v>
+        <v>0.4950690319017436</v>
       </c>
       <c r="H2" t="n">
-        <v>1.176637584587409</v>
+        <v>1.206227248115519</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.132186111237</v>
+        <v>221.4113085736208</v>
       </c>
       <c r="E3" t="n">
-        <v>6536.294022634524</v>
+        <v>6725.59483769013</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2258159937113309</v>
+        <v>0.2358693614871312</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5938175830432354</v>
+        <v>0.5936718064399534</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3802783887840677</v>
+        <v>0.3973059844319693</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.89074887885078</v>
+        <v>0.8906849881866991</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068078695417527</v>
+        <v>1.068082493212163</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.64796333723294</v>
+        <v>37.83003632866814</v>
       </c>
       <c r="E4" t="n">
-        <v>775.5075961506129</v>
+        <v>785.868723860148</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3163889630120496</v>
+        <v>-0.3122939408571156</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5576931905951811</v>
+        <v>0.5578943957749725</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5673172424328744</v>
+        <v>-0.5597725003552103</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7345351754373841</v>
+        <v>0.7349176530081022</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8271853896537597</v>
+        <v>0.8281803416269632</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.60108594232301</v>
+        <v>36.7898629550832</v>
       </c>
       <c r="E5" t="n">
-        <v>1730.086747222041</v>
+        <v>1738.188658021257</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7127771798192157</v>
+        <v>0.724275290928357</v>
       </c>
       <c r="G5" t="n">
-        <v>1.10062873859089</v>
+        <v>1.100605189534674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6476090936274919</v>
+        <v>0.6580700307569637</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.473685306277342</v>
+        <v>0.4736763253378825</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052751034090187</v>
+        <v>1.053046319265748</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.78731395136936</v>
+        <v>10.84142895812051</v>
       </c>
       <c r="E6" t="n">
-        <v>394.3065937772385</v>
+        <v>390.841895957548</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4877328570062611</v>
+        <v>-0.483195124029314</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8102772119451845</v>
+        <v>0.810173958023</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6019333258001786</v>
+        <v>-0.5964091035564939</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6667392092174276</v>
+        <v>0.6666327964239976</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090898980166463</v>
+        <v>1.090935801724642</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.67492227376213</v>
+        <v>10.70610192139726</v>
       </c>
       <c r="E7" t="n">
-        <v>261.4649058761167</v>
+        <v>263.1900660515477</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3175200421287203</v>
+        <v>-0.3124379965687408</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7100515154017487</v>
+        <v>0.709996486096892</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4471788810267756</v>
+        <v>-0.4400556941997357</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.75018514509517</v>
+        <v>0.750165146449009</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075606043798667</v>
+        <v>1.075839092429568</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.438118389872537</v>
+        <v>9.523028488113761</v>
       </c>
       <c r="E8" t="n">
-        <v>427.6395312367392</v>
+        <v>422.4330934933649</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3593014491945443</v>
+        <v>-0.3508663331692963</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164322209211054</v>
+        <v>1.164172917422496</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3085927987562889</v>
+        <v>-0.3013867853463916</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7373162578633264</v>
+        <v>0.7372413691658241</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73349226006507</v>
+        <v>1.733650017027675</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.000808650928733</v>
+        <v>7.019582769473153</v>
       </c>
       <c r="E9" t="n">
-        <v>211.6975194666382</v>
+        <v>211.4751724492881</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3259512147186996</v>
+        <v>0.3311508104018146</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812770469908075</v>
+        <v>0.481306030489151</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6772631621572539</v>
+        <v>0.6880254753202786</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6728674049847231</v>
+        <v>0.6730334958506515</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6539123740531247</v>
+        <v>0.654323052746319</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.819305465429697</v>
+        <v>6.841069733128388</v>
       </c>
       <c r="E10" t="n">
-        <v>744.381568974489</v>
+        <v>753.6582833355312</v>
       </c>
       <c r="F10" t="n">
-        <v>1.000594225541924</v>
+        <v>1.017884498647411</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8164335504828735</v>
+        <v>0.8164723097497679</v>
       </c>
       <c r="H10" t="n">
-        <v>1.225567255228708</v>
+        <v>1.246685878372743</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.663391329921974</v>
+        <v>0.6634676813172086</v>
       </c>
       <c r="N10" t="n">
-        <v>1.093668112051446</v>
+        <v>1.094196880238099</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.376134429579857</v>
+        <v>6.492547026114255</v>
       </c>
       <c r="E11" t="n">
-        <v>286.441553619517</v>
+        <v>125.7250895595708</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3096756747045648</v>
+        <v>-0.2881839600154511</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9522840885480059</v>
+        <v>0.6539440795709437</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3251925328047247</v>
+        <v>-0.4406859378626536</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J11" t="n">
         <v>274</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7130698873017333</v>
+        <v>0.7885503543684634</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371177062649233</v>
+        <v>1.041607942435735</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.168602846198762</v>
+        <v>6.38712267351853</v>
       </c>
       <c r="E12" t="n">
-        <v>125.4680503794765</v>
+        <v>290.4108108243841</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2942782959287031</v>
+        <v>-0.3067137424581036</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6539305957286048</v>
+        <v>0.9522625801278173</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4500145701254739</v>
+        <v>-0.3220894623591478</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J12" t="n">
         <v>274</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7885165094171898</v>
+        <v>0.7131439962422426</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041207680735233</v>
+        <v>1.37172858349799</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.700807886722307</v>
+        <v>4.722167285968768</v>
       </c>
       <c r="E13" t="n">
-        <v>265.0684970996963</v>
+        <v>262.0608429762337</v>
       </c>
       <c r="F13" t="n">
-        <v>1.682344862446713</v>
+        <v>1.700136630589523</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8573566411355266</v>
+        <v>0.8571461748564762</v>
       </c>
       <c r="H13" t="n">
-        <v>1.962246259874456</v>
+        <v>1.983485058279821</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6021548600536438</v>
+        <v>0.601768174824689</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042472547963581</v>
+        <v>1.041881547750934</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.391903735294353</v>
+        <v>4.411354610603251</v>
       </c>
       <c r="E14" t="n">
-        <v>130.1920954070654</v>
+        <v>130.7957528243161</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4277694654467058</v>
+        <v>-0.4223526085915167</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445596713436649</v>
+        <v>0.8444843425420413</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5064999904223931</v>
+        <v>-0.500130774858612</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600982791810307</v>
+        <v>0.7600682264639713</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296268608458272</v>
+        <v>1.296517606942366</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.088759103182626</v>
+        <v>4.12536050473886</v>
       </c>
       <c r="E15" t="n">
-        <v>165.4566420538629</v>
+        <v>167.6521704935342</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4920831979608942</v>
+        <v>0.5026720672625362</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9551793193947071</v>
+        <v>0.9551976852225409</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5151736307196486</v>
+        <v>0.5262492518974481</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5133340121674655</v>
+        <v>0.5134051488234895</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9901018373798076</v>
+        <v>0.9905758149600069</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.017327960966846</v>
+        <v>4.035611879807006</v>
       </c>
       <c r="E16" t="n">
-        <v>254.1309358311068</v>
+        <v>244.0663412230761</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06623820741820696</v>
+        <v>-0.0582293763546502</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7897949685805995</v>
+        <v>0.7897032736372777</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.08386759862151144</v>
+        <v>-0.07373576670950437</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131515097039486</v>
+        <v>0.7130769875648324</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137342017123703</v>
+        <v>1.137455981183487</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.747753805906791</v>
+        <v>3.810752585097569</v>
       </c>
       <c r="E17" t="n">
-        <v>148.9762854775578</v>
+        <v>143.1389486472736</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.08818372313789602</v>
+        <v>-0.06679910588444049</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7509295735840554</v>
+        <v>0.751020283604701</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1174327476770032</v>
+        <v>-0.08894447639126636</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7206521292143403</v>
+        <v>0.7203224743041564</v>
       </c>
       <c r="N17" t="n">
-        <v>1.092747439419237</v>
+        <v>1.092730011531231</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.030591908751319</v>
+        <v>3.054481723961704</v>
       </c>
       <c r="E18" t="n">
-        <v>79.21269431821187</v>
+        <v>79.8506244742246</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.482241005321402</v>
+        <v>-0.4748856182286382</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7408644568395341</v>
+        <v>0.7407159889295544</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6509166432124466</v>
+        <v>-0.6411170074982708</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645223358192181</v>
+        <v>0.7643951549415275</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143730895872879</v>
+        <v>1.143678308761287</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.886883942303643</v>
+        <v>2.91356251001051</v>
       </c>
       <c r="E19" t="n">
-        <v>109.6324789639413</v>
+        <v>114.4734549089072</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06914429185361737</v>
+        <v>0.08729080989429905</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4790415250286487</v>
+        <v>0.4784086703112819</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1443388270974677</v>
+        <v>0.1824607606661943</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7174378977233961</v>
+        <v>0.7173107461878944</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6939886860206628</v>
+        <v>0.693171372415499</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.589005534277344</v>
+        <v>2.594167409044904</v>
       </c>
       <c r="E20" t="n">
-        <v>128.6760293984987</v>
+        <v>130.8438638889811</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3177170938181112</v>
+        <v>-0.3152190309179096</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7733866274947238</v>
+        <v>0.7733191736626841</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4108127584870592</v>
+        <v>-0.4076182792997781</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7322290763126159</v>
+        <v>0.7321042298563092</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143506253460265</v>
+        <v>1.143578373085959</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.0266199688078</v>
+        <v>567.8031180131703</v>
       </c>
       <c r="E2" t="n">
-        <v>15757.35906729426</v>
+        <v>16589.37985713564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5971657559780541</v>
+        <v>0.6025723223379205</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4950690319017436</v>
+        <v>0.4950409890144801</v>
       </c>
       <c r="H2" t="n">
-        <v>1.206227248115519</v>
+        <v>1.217217029922132</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.4113085736208</v>
+        <v>222.2986298899415</v>
       </c>
       <c r="E3" t="n">
-        <v>6725.59483769013</v>
+        <v>6976.838752780191</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2358693614871312</v>
+        <v>0.2404612710844982</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5936718064399534</v>
+        <v>0.5936324025006581</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3973059844319693</v>
+        <v>0.405067631199986</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906849881866991</v>
+        <v>0.8906701332387458</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068082493212163</v>
+        <v>1.068054287954391</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.83003632866814</v>
+        <v>37.90795503735794</v>
       </c>
       <c r="E4" t="n">
-        <v>785.868723860148</v>
+        <v>798.7304144932027</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3122939408571156</v>
+        <v>-0.3111760591989535</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5578943957749725</v>
+        <v>0.5579577714297697</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5597725003552103</v>
+        <v>-0.5577053948035589</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7349176530081022</v>
+        <v>0.7351113015575284</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8281803416269632</v>
+        <v>0.8285396011074113</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.7898629550832</v>
+        <v>36.80549009336921</v>
       </c>
       <c r="E5" t="n">
-        <v>1738.188658021257</v>
+        <v>1576.349967137999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.724275290928357</v>
+        <v>0.7223028245023027</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100605189534674</v>
+        <v>1.100607092398685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6580700307569637</v>
+        <v>0.6562767308069051</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736763253378825</v>
+        <v>0.4736996909392177</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053046319265748</v>
+        <v>1.053159740474578</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.84142895812051</v>
+        <v>10.8440391017868</v>
       </c>
       <c r="E6" t="n">
-        <v>390.841895957548</v>
+        <v>368.4443084445841</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.483195124029314</v>
+        <v>-0.4841746943038866</v>
       </c>
       <c r="G6" t="n">
-        <v>0.810173958023</v>
+        <v>0.8101903444446681</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5964091035564939</v>
+        <v>-0.5976061028421121</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666327964239976</v>
+        <v>0.6666171152878998</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090935801724642</v>
+        <v>1.090994002987532</v>
       </c>
     </row>
     <row r="7">
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.70610192139726</v>
+        <v>10.72044282590444</v>
       </c>
       <c r="E7" t="n">
-        <v>263.1900660515477</v>
+        <v>257.0686218015396</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3124379965687408</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.750165146449009</v>
+        <v>0.7501830323958982</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075839092429568</v>
+        <v>1.075925688478735</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.523028488113761</v>
+        <v>9.519372023172101</v>
       </c>
       <c r="E8" t="n">
-        <v>422.4330934933649</v>
+        <v>414.0791758611867</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3508663331692963</v>
+        <v>-0.3519681243372096</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164172917422496</v>
+        <v>1.164186378864148</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3013867853463916</v>
+        <v>-0.3023297048713208</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372413691658241</v>
+        <v>0.7372322144320249</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733650017027675</v>
+        <v>1.73374674248744</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.019582769473153</v>
+        <v>7.010640971053239</v>
       </c>
       <c r="E9" t="n">
-        <v>211.4751724492881</v>
+        <v>209.9267134200468</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3311508104018146</v>
+        <v>0.327759194234555</v>
       </c>
       <c r="G9" t="n">
-        <v>0.481306030489151</v>
+        <v>0.4812844306520518</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6880254753202786</v>
+        <v>0.6810093436650374</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6730334958506515</v>
+        <v>0.6732035120071771</v>
       </c>
       <c r="N9" t="n">
-        <v>0.654323052746319</v>
+        <v>0.654496044124255</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.841069733128388</v>
+        <v>6.847893420902051</v>
       </c>
       <c r="E10" t="n">
-        <v>753.6582833355312</v>
+        <v>753.4005844113666</v>
       </c>
       <c r="F10" t="n">
-        <v>1.017884498647411</v>
+        <v>1.014423477658255</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8164723097497679</v>
+        <v>0.8164591156071662</v>
       </c>
       <c r="H10" t="n">
-        <v>1.246685878372743</v>
+        <v>1.242466962848312</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6634676813172086</v>
+        <v>0.6635855026899937</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094196880238099</v>
+        <v>1.094435500653384</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>MATIC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Polygon</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.492547026114255</v>
+        <v>6.399869177178122</v>
       </c>
       <c r="E11" t="n">
-        <v>125.7250895595708</v>
+        <v>283.6372440906929</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2881839600154511</v>
+        <v>-0.3068484443094953</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6539440795709437</v>
+        <v>0.9522632514662441</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4406859378626536</v>
+        <v>-0.3222306897142428</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.6126386245816655</v>
       </c>
       <c r="J11" t="n">
         <v>274</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7885503543684634</v>
+        <v>0.7131619847401551</v>
       </c>
       <c r="N11" t="n">
-        <v>1.041607942435735</v>
+        <v>1.371841858515104</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MATIC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.38712267351853</v>
+        <v>6.215359171312463</v>
       </c>
       <c r="E12" t="n">
-        <v>290.4108108243841</v>
+        <v>121.0741547124921</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3067137424581036</v>
+        <v>-0.2883688286829766</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9522625801278173</v>
+        <v>0.6539424394006773</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3220894623591478</v>
+        <v>-0.4409697418434256</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6126386245816655</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J12" t="n">
         <v>274</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7131439962422426</v>
+        <v>0.7886431518248956</v>
       </c>
       <c r="N12" t="n">
-        <v>1.37172858349799</v>
+        <v>1.041786918589737</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.722167285968768</v>
+        <v>4.701462295112337</v>
       </c>
       <c r="E13" t="n">
-        <v>262.0608429762337</v>
+        <v>256.2342393482065</v>
       </c>
       <c r="F13" t="n">
-        <v>1.700136630589523</v>
+        <v>1.685308119941396</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8571461748564762</v>
+        <v>0.8573190732440166</v>
       </c>
       <c r="H13" t="n">
-        <v>1.983485058279821</v>
+        <v>1.965788669047505</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.601768174824689</v>
+        <v>0.6015139758256978</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041881547750934</v>
+        <v>1.041710516385395</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.411354610603251</v>
+        <v>4.409656647366842</v>
       </c>
       <c r="E14" t="n">
-        <v>130.7957528243161</v>
+        <v>120.0820201524359</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4223526085915167</v>
+        <v>-0.4241596409500312</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8444843425420413</v>
+        <v>0.8445009333506084</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.500130774858612</v>
+        <v>-0.5022607130428527</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600682264639713</v>
+        <v>0.7600908197301892</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296517606942366</v>
+        <v>1.296655066828412</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.12536050473886</v>
+        <v>4.123451165243549</v>
       </c>
       <c r="E15" t="n">
-        <v>167.6521704935342</v>
+        <v>164.6457940413105</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5026720672625362</v>
+        <v>0.5013474380992351</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9551976852225409</v>
+        <v>0.9551932498486178</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5262492518974481</v>
+        <v>0.5248649298753842</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5134051488234895</v>
+        <v>0.5134783585731589</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9905758149600069</v>
+        <v>0.9907685887361601</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.035611879807006</v>
+        <v>4.050202623388154</v>
       </c>
       <c r="E16" t="n">
-        <v>244.0663412230761</v>
+        <v>225.1577203512827</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0582293763546502</v>
+        <v>-0.05689291484770964</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7897032736372777</v>
+        <v>0.7896945333677582</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.07373576670950437</v>
+        <v>-0.07204420499795304</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7130769875648324</v>
+        <v>0.7130682512569725</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137455981183487</v>
+        <v>1.137493889257051</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.810752585097569</v>
+        <v>3.835101983390885</v>
       </c>
       <c r="E17" t="n">
-        <v>143.1389486472736</v>
+        <v>146.7505426534915</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06679910588444049</v>
+        <v>-0.05964352316370669</v>
       </c>
       <c r="G17" t="n">
-        <v>0.751020283604701</v>
+        <v>0.7511690634363373</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08894447639126636</v>
+        <v>-0.07940093125089352</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7203224743041564</v>
+        <v>0.7202653495771331</v>
       </c>
       <c r="N17" t="n">
-        <v>1.092730011531231</v>
+        <v>1.092921717744216</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.054481723961704</v>
+        <v>3.064514653406416</v>
       </c>
       <c r="E18" t="n">
-        <v>79.8506244742246</v>
+        <v>77.72754912507607</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4748856182286382</v>
+        <v>-0.4743309415553305</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407159889295544</v>
+        <v>0.7407127178511416</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6411170074982708</v>
+        <v>-0.6403709969114573</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7643951549415275</v>
+        <v>0.7644088456636435</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143678308761287</v>
+        <v>1.143758529466758</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.91356251001051</v>
+        <v>2.912610323187016</v>
       </c>
       <c r="E19" t="n">
-        <v>114.4734549089072</v>
+        <v>114.1606045756573</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08729080989429905</v>
+        <v>0.08547273545901257</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4784086703112819</v>
+        <v>0.4784529718750745</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1824607606661943</v>
+        <v>0.178643963949146</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7173107461878944</v>
+        <v>0.7171311870654149</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693171372415499</v>
+        <v>0.693101289165596</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.594167409044904</v>
+        <v>2.601284872844075</v>
       </c>
       <c r="E20" t="n">
-        <v>130.8438638889811</v>
+        <v>129.3070848420864</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3152190309179096</v>
+        <v>-0.3142191687918265</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7733191736626841</v>
+        <v>0.7732956655392681</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4076182792997781</v>
+        <v>-0.4063376827189398</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321042298563092</v>
+        <v>0.7320413129906557</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143578373085959</v>
+        <v>1.14351010702831</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-01.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.8031180131703</v>
+        <v>567.8587749091812</v>
       </c>
       <c r="E2" t="n">
-        <v>16589.37985713564</v>
+        <v>16543.04003705529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6025723223379205</v>
+        <v>0.6042419171063844</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4950409890144801</v>
+        <v>0.4950357655464849</v>
       </c>
       <c r="H2" t="n">
-        <v>1.217217029922132</v>
+        <v>1.220602548665031</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.2986298899415</v>
+        <v>222.1605776231442</v>
       </c>
       <c r="E3" t="n">
-        <v>6976.838752780191</v>
+        <v>6938.661580977654</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2404612710844982</v>
+        <v>0.2411674077850392</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5936324025006581</v>
+        <v>0.5936278507858267</v>
       </c>
       <c r="H3" t="n">
-        <v>0.405067631199986</v>
+        <v>0.4062602646856764</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906701332387458</v>
+        <v>0.8906646933397954</v>
       </c>
       <c r="N3" t="n">
-        <v>1.068054287954391</v>
+        <v>1.068050844961568</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.90795503735794</v>
+        <v>37.80764309554839</v>
       </c>
       <c r="E4" t="n">
-        <v>798.7304144932027</v>
+        <v>797.2970077422773</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3111760591989535</v>
+        <v>-0.3122939408571156</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5579577714297697</v>
+        <v>0.5578943957749725</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5577053948035589</v>
+        <v>-0.5597725003552103</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7351113015575284</v>
+        <v>0.7352978145752815</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8285396011074113</v>
+        <v>0.8286644289716759</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.80549009336921</v>
+        <v>37.08582734755879</v>
       </c>
       <c r="E5" t="n">
-        <v>1576.349967137999</v>
+        <v>1423.750161145744</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7223028245023027</v>
+        <v>0.7410639425087435</v>
       </c>
       <c r="G5" t="n">
-        <v>1.100607092398685</v>
+        <v>1.100624670171115</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6562767308069051</v>
+        <v>0.6733121313676619</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736996909392177</v>
+        <v>0.4736508646307317</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053159740474578</v>
+        <v>1.053079116586598</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.8440391017868</v>
+        <v>10.9248743420571</v>
       </c>
       <c r="E6" t="n">
-        <v>368.4443084445841</v>
+        <v>354.9445977261477</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4841746943038866</v>
+        <v>-0.4802536362111314</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8101903444446681</v>
+        <v>0.8101442191574214</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5976061028421121</v>
+        <v>-0.5928001766285663</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666171152878998</v>
+        <v>0.6666025715901642</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090994002987532</v>
+        <v>1.090919601037456</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.72044282590444</v>
+        <v>10.74723956185537</v>
       </c>
       <c r="E7" t="n">
-        <v>257.0686218015396</v>
+        <v>246.8973309038426</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3124379965687408</v>
+        <v>-0.3094441729585747</v>
       </c>
       <c r="G7" t="n">
-        <v>0.709996486096892</v>
+        <v>0.7099906211614885</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4400556941997357</v>
+        <v>-0.4358426206424369</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501830323958982</v>
+        <v>0.7501636194800573</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075925688478735</v>
+        <v>1.07590031112082</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.519372023172101</v>
+        <v>9.561340563181551</v>
       </c>
       <c r="E8" t="n">
-        <v>414.0791758611867</v>
+        <v>410.26132467705</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3519681243372096</v>
+        <v>-0.3482936738581096</v>
       </c>
       <c r="G8" t="n">
-        <v>1.164186378864148</v>
+        <v>1.164148521621035</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3023297048713208</v>
+        <v>-0.2991831947465974</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372322144320249</v>
+        <v>0.7372255840814924</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73374674248744</v>
+        <v>1.733693065312637</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.010640971053239</v>
+        <v>7.000469639721675</v>
       </c>
       <c r="E9" t="n">
-        <v>209.9267134200468</v>
+        <v>210.1482769608886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.327759194234555</v>
+        <v>0.3252733807810715</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4812844306520518</v>
+        <v>0.4812750199880165</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6810093436650374</v>
+        <v>0.67585760172878</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6732035120071771</v>
+        <v>0.6732539146468174</v>
       </c>
       <c r="N9" t="n">
-        <v>0.654496044124255</v>
+        <v>0.6545391540972028</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.847893420902051</v>
+        <v>6.852439299899669</v>
       </c>
       <c r="E10" t="n">
-        <v>753.4005844113666</v>
+        <v>753.8713244439703</v>
       </c>
       <c r="F10" t="n">
-        <v>1.014423477658255</v>
+        <v>1.020192668624393</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8164591156071662</v>
+        <v>0.8164826174772006</v>
       </c>
       <c r="H10" t="n">
-        <v>1.242466962848312</v>
+        <v>1.249497107209242</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6635855026899937</v>
+        <v>0.6635727570126169</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094435500653384</v>
+        <v>1.094457530627346</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.399869177178122</v>
+        <v>6.404672228724506</v>
       </c>
       <c r="E11" t="n">
-        <v>283.6372440906929</v>
+        <v>284.4761645711549</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3068484443094953</v>
+        <v>-0.3042879939127363</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9522632514662441</v>
+        <v>0.9522554847731338</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3222306897142428</v>
+        <v>-0.3195444907153568</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7131619847401551</v>
+        <v>0.7131514863024538</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371841858515104</v>
+        <v>1.371824949972942</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.215359171312463</v>
+        <v>6.23324821243276</v>
       </c>
       <c r="E12" t="n">
-        <v>121.0741547124921</v>
+        <v>120.1232882360338</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2883688286829766</v>
+        <v>-0.2848542784433896</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6539424394006773</v>
+        <v>0.6539867636222307</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4409697418434256</v>
+        <v>-0.4355658161423172</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7886431518248956</v>
+        <v>0.7885787911794595</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041786918589737</v>
+        <v>1.041783498077693</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.701462295112337</v>
+        <v>4.715907005137343</v>
       </c>
       <c r="E13" t="n">
-        <v>256.2342393482065</v>
+        <v>247.4419852730088</v>
       </c>
       <c r="F13" t="n">
-        <v>1.685308119941396</v>
+        <v>1.700136630589523</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8573190732440166</v>
+        <v>0.8571461748564762</v>
       </c>
       <c r="H13" t="n">
-        <v>1.965788669047505</v>
+        <v>1.983485058279821</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6015139758256978</v>
+        <v>0.6015425546884703</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041710516385395</v>
+        <v>1.041560904585182</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.409656647366842</v>
+        <v>4.410461738866441</v>
       </c>
       <c r="E14" t="n">
-        <v>120.0820201524359</v>
+        <v>116.1767131609518</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4241596409500312</v>
+        <v>-0.423557453683597</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8445009333506084</v>
+        <v>0.8444944564904024</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5022607130428527</v>
+        <v>-0.5015514908692721</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600908197301892</v>
+        <v>0.7600853920833243</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296655066828412</v>
+        <v>1.296649544836628</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.123451165243549</v>
+        <v>4.142512315225106</v>
       </c>
       <c r="E15" t="n">
-        <v>164.6457940413105</v>
+        <v>152.4983213854285</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5013474380992351</v>
+        <v>0.5066477013457591</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9551932498486178</v>
+        <v>0.9552146591464035</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5248649298753842</v>
+        <v>0.5304019326907193</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5134783585731589</v>
+        <v>0.5134662620247817</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9907685887361601</v>
+        <v>0.9907779085855233</v>
       </c>
     </row>
     <row r="16">
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.050202623388154</v>
+        <v>4.045959869140008</v>
       </c>
       <c r="E16" t="n">
-        <v>225.1577203512827</v>
+        <v>219.9178896692744</v>
       </c>
       <c r="F16" t="n">
         <v>-0.05689291484770964</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7130682512569725</v>
+        <v>0.7130641582808331</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137493889257051</v>
+        <v>1.137499362522281</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.835101983390885</v>
+        <v>3.813401265884611</v>
       </c>
       <c r="E17" t="n">
-        <v>146.7505426534915</v>
+        <v>144.416454829752</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.05964352316370669</v>
+        <v>-0.0679276879981412</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7511690634363373</v>
+        <v>0.7510022084425625</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.07940093125089352</v>
+        <v>-0.09044938514762887</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7202653495771331</v>
+        <v>0.7205320636659761</v>
       </c>
       <c r="N17" t="n">
-        <v>1.092921717744216</v>
+        <v>1.093095102874971</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.064514653406416</v>
+        <v>3.065886274092106</v>
       </c>
       <c r="E18" t="n">
-        <v>77.72754912507607</v>
+        <v>76.368312680278</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4743309415553305</v>
+        <v>-0.4733797277234072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7407127178511416</v>
+        <v>0.7407096850695337</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6403709969114573</v>
+        <v>-0.6390894263505802</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644088456636435</v>
+        <v>0.7644042808933531</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143758529466758</v>
+        <v>1.143759084843641</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.912610323187016</v>
+        <v>2.91889521766969</v>
       </c>
       <c r="E19" t="n">
-        <v>114.1606045756573</v>
+        <v>114.7125539552582</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08547273545901257</v>
+        <v>0.08820013149210171</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4784529718750745</v>
+        <v>0.4783881033712594</v>
       </c>
       <c r="H19" t="n">
-        <v>0.178643963949146</v>
+        <v>0.1843694081657646</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7171311870654149</v>
+        <v>0.7171549836212451</v>
       </c>
       <c r="N19" t="n">
-        <v>0.693101289165596</v>
+        <v>0.693037627410778</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.601284872844075</v>
+        <v>2.605180141656225</v>
       </c>
       <c r="E20" t="n">
-        <v>129.3070848420864</v>
+        <v>128.1004097671734</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3142191687918265</v>
+        <v>-0.311217401988223</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7732956655392681</v>
+        <v>0.7732370523297685</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4063376827189398</v>
+        <v>-0.4024864057542547</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320413129906557</v>
+        <v>0.7320479622212203</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14351010702831</v>
+        <v>1.143445883848562</v>
       </c>
     </row>
   </sheetData>
